--- a/test/バーコードテストデータ.xlsx
+++ b/test/バーコードテストデータ.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12570" firstSheet="19" activeTab="24"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12570" firstSheet="20" activeTab="25"/>
   </bookViews>
   <sheets>
     <sheet name="ｵﾘｴﾝﾄ" sheetId="1" r:id="rId1"/>
@@ -37,9 +37,10 @@
     <sheet name="C0104臨海" sheetId="27" r:id="rId23"/>
     <sheet name="15628-32112" sheetId="28" r:id="rId24"/>
     <sheet name="v250809" sheetId="29" r:id="rId25"/>
-    <sheet name="朝一校正" sheetId="21" r:id="rId26"/>
-    <sheet name="v241104ラミネート" sheetId="17" r:id="rId27"/>
-    <sheet name="WPA2" sheetId="18" r:id="rId28"/>
+    <sheet name="v251122" sheetId="30" r:id="rId26"/>
+    <sheet name="朝一校正" sheetId="21" r:id="rId27"/>
+    <sheet name="v241104ラミネート" sheetId="17" r:id="rId28"/>
+    <sheet name="WPA2" sheetId="18" r:id="rId29"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
@@ -62,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="516" uniqueCount="291">
   <si>
     <t>32A35-06401</t>
     <phoneticPr fontId="1"/>
@@ -1876,6 +1877,26 @@
     <t xml:space="preserve">28T18557074378187408001601- -  ｶﾝﾄ-ｳ-ｻﾝ0000060ML   0000060                      20250821            </t>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t xml:space="preserve">28T18557064284026244001601- -  ｶﾝﾄ-ｳ-ｻﾝ0000040ML   0000040                      20251126            </t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">28T18557074384026277001601- -  ｶﾝﾄ-ｳ-ｻﾝ0000040ML   0000040                      20251126            </t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>KQR_Tag|Z019808491|3S20053064R|8|ZWSA0C|4506891869|00010|3S20053064||1004012|8|B2|19226|20251125||06891869|4506891869|</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>213S2005307360008</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3S200-53073</t>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
@@ -2284,7 +2305,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2432,6 +2453,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2537,8 +2564,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -4113,8 +4140,8 @@
 
 <file path=xl/activeX/activeX187.xml><?xml version="1.0" encoding="utf-8"?>
 <ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{D9347033-9612-11D1-9D75-00C04FCC8CDC}" ax:persistence="persistPropertyBag">
-  <ax:ocxPr ax:name="_cx" ax:value="3307"/>
-  <ax:ocxPr ax:name="_cy" ax:value="3307"/>
+  <ax:ocxPr ax:name="_cx" ax:value="3300"/>
+  <ax:ocxPr ax:name="_cy" ax:value="3300"/>
   <ax:ocxPr ax:name="Style" ax:value="11"/>
   <ax:ocxPr ax:name="SubStyle" ax:value="-1"/>
   <ax:ocxPr ax:name="Validation" ax:value="2"/>
@@ -4129,8 +4156,8 @@
 
 <file path=xl/activeX/activeX188.xml><?xml version="1.0" encoding="utf-8"?>
 <ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{D9347033-9612-11D1-9D75-00C04FCC8CDC}" ax:persistence="persistPropertyBag">
-  <ax:ocxPr ax:name="_cx" ax:value="3307"/>
-  <ax:ocxPr ax:name="_cy" ax:value="3307"/>
+  <ax:ocxPr ax:name="_cx" ax:value="3300"/>
+  <ax:ocxPr ax:name="_cy" ax:value="3300"/>
   <ax:ocxPr ax:name="Style" ax:value="11"/>
   <ax:ocxPr ax:name="SubStyle" ax:value="0"/>
   <ax:ocxPr ax:name="Validation" ax:value="2"/>
@@ -4145,8 +4172,8 @@
 
 <file path=xl/activeX/activeX189.xml><?xml version="1.0" encoding="utf-8"?>
 <ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{D9347033-9612-11D1-9D75-00C04FCC8CDC}" ax:persistence="persistPropertyBag">
-  <ax:ocxPr ax:name="_cx" ax:value="3307"/>
-  <ax:ocxPr ax:name="_cy" ax:value="3307"/>
+  <ax:ocxPr ax:name="_cx" ax:value="3300"/>
+  <ax:ocxPr ax:name="_cy" ax:value="3300"/>
   <ax:ocxPr ax:name="Style" ax:value="11"/>
   <ax:ocxPr ax:name="SubStyle" ax:value="0"/>
   <ax:ocxPr ax:name="Validation" ax:value="2"/>
@@ -4177,8 +4204,8 @@
 
 <file path=xl/activeX/activeX190.xml><?xml version="1.0" encoding="utf-8"?>
 <ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{D9347033-9612-11D1-9D75-00C04FCC8CDC}" ax:persistence="persistPropertyBag">
-  <ax:ocxPr ax:name="_cx" ax:value="3307"/>
-  <ax:ocxPr ax:name="_cy" ax:value="3307"/>
+  <ax:ocxPr ax:name="_cx" ax:value="3300"/>
+  <ax:ocxPr ax:name="_cy" ax:value="3300"/>
   <ax:ocxPr ax:name="Style" ax:value="11"/>
   <ax:ocxPr ax:name="SubStyle" ax:value="-1"/>
   <ax:ocxPr ax:name="Validation" ax:value="2"/>
@@ -4193,8 +4220,8 @@
 
 <file path=xl/activeX/activeX191.xml><?xml version="1.0" encoding="utf-8"?>
 <ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{D9347033-9612-11D1-9D75-00C04FCC8CDC}" ax:persistence="persistPropertyBag">
-  <ax:ocxPr ax:name="_cx" ax:value="3307"/>
-  <ax:ocxPr ax:name="_cy" ax:value="3307"/>
+  <ax:ocxPr ax:name="_cx" ax:value="3300"/>
+  <ax:ocxPr ax:name="_cy" ax:value="3300"/>
   <ax:ocxPr ax:name="Style" ax:value="11"/>
   <ax:ocxPr ax:name="SubStyle" ax:value="-1"/>
   <ax:ocxPr ax:name="Validation" ax:value="2"/>
@@ -4209,8 +4236,8 @@
 
 <file path=xl/activeX/activeX192.xml><?xml version="1.0" encoding="utf-8"?>
 <ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{D9347033-9612-11D1-9D75-00C04FCC8CDC}" ax:persistence="persistPropertyBag">
-  <ax:ocxPr ax:name="_cx" ax:value="10319"/>
-  <ax:ocxPr ax:name="_cy" ax:value="2858"/>
+  <ax:ocxPr ax:name="_cx" ax:value="4780"/>
+  <ax:ocxPr ax:name="_cy" ax:value="1600"/>
   <ax:ocxPr ax:name="Style" ax:value="7"/>
   <ax:ocxPr ax:name="SubStyle" ax:value="-1"/>
   <ax:ocxPr ax:name="Validation" ax:value="0"/>
@@ -4225,8 +4252,8 @@
 
 <file path=xl/activeX/activeX193.xml><?xml version="1.0" encoding="utf-8"?>
 <ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{D9347033-9612-11D1-9D75-00C04FCC8CDC}" ax:persistence="persistPropertyBag">
-  <ax:ocxPr ax:name="_cx" ax:value="4842"/>
-  <ax:ocxPr ax:name="_cy" ax:value="4498"/>
+  <ax:ocxPr ax:name="_cx" ax:value="3300"/>
+  <ax:ocxPr ax:name="_cy" ax:value="3300"/>
   <ax:ocxPr ax:name="Style" ax:value="11"/>
   <ax:ocxPr ax:name="SubStyle" ax:value="-1"/>
   <ax:ocxPr ax:name="Validation" ax:value="2"/>
@@ -4241,8 +4268,8 @@
 
 <file path=xl/activeX/activeX194.xml><?xml version="1.0" encoding="utf-8"?>
 <ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{D9347033-9612-11D1-9D75-00C04FCC8CDC}" ax:persistence="persistPropertyBag">
-  <ax:ocxPr ax:name="_cx" ax:value="3307"/>
-  <ax:ocxPr ax:name="_cy" ax:value="3334"/>
+  <ax:ocxPr ax:name="_cx" ax:value="3300"/>
+  <ax:ocxPr ax:name="_cy" ax:value="3300"/>
   <ax:ocxPr ax:name="Style" ax:value="11"/>
   <ax:ocxPr ax:name="SubStyle" ax:value="0"/>
   <ax:ocxPr ax:name="Validation" ax:value="2"/>
@@ -4257,8 +4284,8 @@
 
 <file path=xl/activeX/activeX195.xml><?xml version="1.0" encoding="utf-8"?>
 <ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{D9347033-9612-11D1-9D75-00C04FCC8CDC}" ax:persistence="persistPropertyBag">
-  <ax:ocxPr ax:name="_cx" ax:value="4419"/>
-  <ax:ocxPr ax:name="_cy" ax:value="4207"/>
+  <ax:ocxPr ax:name="_cx" ax:value="3300"/>
+  <ax:ocxPr ax:name="_cy" ax:value="3300"/>
   <ax:ocxPr ax:name="Style" ax:value="11"/>
   <ax:ocxPr ax:name="SubStyle" ax:value="-1"/>
   <ax:ocxPr ax:name="Validation" ax:value="2"/>
@@ -4273,8 +4300,8 @@
 
 <file path=xl/activeX/activeX196.xml><?xml version="1.0" encoding="utf-8"?>
 <ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{D9347033-9612-11D1-9D75-00C04FCC8CDC}" ax:persistence="persistPropertyBag">
-  <ax:ocxPr ax:name="_cx" ax:value="4842"/>
-  <ax:ocxPr ax:name="_cy" ax:value="4498"/>
+  <ax:ocxPr ax:name="_cx" ax:value="3300"/>
+  <ax:ocxPr ax:name="_cy" ax:value="3300"/>
   <ax:ocxPr ax:name="Style" ax:value="11"/>
   <ax:ocxPr ax:name="SubStyle" ax:value="-1"/>
   <ax:ocxPr ax:name="Validation" ax:value="2"/>
@@ -4289,8 +4316,8 @@
 
 <file path=xl/activeX/activeX197.xml><?xml version="1.0" encoding="utf-8"?>
 <ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{D9347033-9612-11D1-9D75-00C04FCC8CDC}" ax:persistence="persistPropertyBag">
-  <ax:ocxPr ax:name="_cx" ax:value="4419"/>
-  <ax:ocxPr ax:name="_cy" ax:value="4207"/>
+  <ax:ocxPr ax:name="_cx" ax:value="3300"/>
+  <ax:ocxPr ax:name="_cy" ax:value="3300"/>
   <ax:ocxPr ax:name="Style" ax:value="11"/>
   <ax:ocxPr ax:name="SubStyle" ax:value="0"/>
   <ax:ocxPr ax:name="Validation" ax:value="2"/>
@@ -4305,8 +4332,8 @@
 
 <file path=xl/activeX/activeX198.xml><?xml version="1.0" encoding="utf-8"?>
 <ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{D9347033-9612-11D1-9D75-00C04FCC8CDC}" ax:persistence="persistPropertyBag">
-  <ax:ocxPr ax:name="_cx" ax:value="3307"/>
-  <ax:ocxPr ax:name="_cy" ax:value="3334"/>
+  <ax:ocxPr ax:name="_cx" ax:value="3300"/>
+  <ax:ocxPr ax:name="_cy" ax:value="3300"/>
   <ax:ocxPr ax:name="Style" ax:value="11"/>
   <ax:ocxPr ax:name="SubStyle" ax:value="0"/>
   <ax:ocxPr ax:name="Validation" ax:value="2"/>
@@ -4321,8 +4348,8 @@
 
 <file path=xl/activeX/activeX199.xml><?xml version="1.0" encoding="utf-8"?>
 <ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{D9347033-9612-11D1-9D75-00C04FCC8CDC}" ax:persistence="persistPropertyBag">
-  <ax:ocxPr ax:name="_cx" ax:value="3307"/>
-  <ax:ocxPr ax:name="_cy" ax:value="3334"/>
+  <ax:ocxPr ax:name="_cx" ax:value="3300"/>
+  <ax:ocxPr ax:name="_cy" ax:value="3300"/>
   <ax:ocxPr ax:name="Style" ax:value="11"/>
   <ax:ocxPr ax:name="SubStyle" ax:value="-1"/>
   <ax:ocxPr ax:name="Validation" ax:value="2"/>
@@ -4369,8 +4396,8 @@
 
 <file path=xl/activeX/activeX200.xml><?xml version="1.0" encoding="utf-8"?>
 <ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{D9347033-9612-11D1-9D75-00C04FCC8CDC}" ax:persistence="persistPropertyBag">
-  <ax:ocxPr ax:name="_cx" ax:value="4842"/>
-  <ax:ocxPr ax:name="_cy" ax:value="4498"/>
+  <ax:ocxPr ax:name="_cx" ax:value="3300"/>
+  <ax:ocxPr ax:name="_cy" ax:value="3300"/>
   <ax:ocxPr ax:name="Style" ax:value="11"/>
   <ax:ocxPr ax:name="SubStyle" ax:value="0"/>
   <ax:ocxPr ax:name="Validation" ax:value="2"/>
@@ -4385,15 +4412,15 @@
 
 <file path=xl/activeX/activeX201.xml><?xml version="1.0" encoding="utf-8"?>
 <ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{D9347033-9612-11D1-9D75-00C04FCC8CDC}" ax:persistence="persistPropertyBag">
-  <ax:ocxPr ax:name="_cx" ax:value="3300"/>
-  <ax:ocxPr ax:name="_cy" ax:value="3300"/>
+  <ax:ocxPr ax:name="_cx" ax:value="4419"/>
+  <ax:ocxPr ax:name="_cy" ax:value="4207"/>
   <ax:ocxPr ax:name="Style" ax:value="11"/>
-  <ax:ocxPr ax:name="SubStyle" ax:value="-1"/>
+  <ax:ocxPr ax:name="SubStyle" ax:value="0"/>
   <ax:ocxPr ax:name="Validation" ax:value="2"/>
-  <ax:ocxPr ax:name="LineWeight" ax:value="3"/>
+  <ax:ocxPr ax:name="LineWeight" ax:value="1"/>
   <ax:ocxPr ax:name="Direction" ax:value="0"/>
   <ax:ocxPr ax:name="ShowData" ax:value="1"/>
-  <ax:ocxPr ax:name="Value" ax:value="PROOFREAD-OK"/>
+  <ax:ocxPr ax:name="Value" ax:value="213S2005307360008"/>
   <ax:ocxPr ax:name="ForeColor" ax:value="0"/>
   <ax:ocxPr ax:name="BackColor" ax:value="16777215"/>
 </ax:ocx>
@@ -4401,15 +4428,15 @@
 
 <file path=xl/activeX/activeX202.xml><?xml version="1.0" encoding="utf-8"?>
 <ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{D9347033-9612-11D1-9D75-00C04FCC8CDC}" ax:persistence="persistPropertyBag">
-  <ax:ocxPr ax:name="_cx" ax:value="3300"/>
-  <ax:ocxPr ax:name="_cy" ax:value="3300"/>
+  <ax:ocxPr ax:name="_cx" ax:value="4842"/>
+  <ax:ocxPr ax:name="_cy" ax:value="4498"/>
   <ax:ocxPr ax:name="Style" ax:value="11"/>
   <ax:ocxPr ax:name="SubStyle" ax:value="0"/>
   <ax:ocxPr ax:name="Validation" ax:value="2"/>
-  <ax:ocxPr ax:name="LineWeight" ax:value="3"/>
+  <ax:ocxPr ax:name="LineWeight" ax:value="1"/>
   <ax:ocxPr ax:name="Direction" ax:value="0"/>
   <ax:ocxPr ax:name="ShowData" ax:value="1"/>
-  <ax:ocxPr ax:name="Value" ax:value="PROOFREAD-NG"/>
+  <ax:ocxPr ax:name="Value" ax:value="3S200-53073"/>
   <ax:ocxPr ax:name="ForeColor" ax:value="0"/>
   <ax:ocxPr ax:name="BackColor" ax:value="16777215"/>
 </ax:ocx>
@@ -4417,15 +4444,15 @@
 
 <file path=xl/activeX/activeX203.xml><?xml version="1.0" encoding="utf-8"?>
 <ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{D9347033-9612-11D1-9D75-00C04FCC8CDC}" ax:persistence="persistPropertyBag">
-  <ax:ocxPr ax:name="_cx" ax:value="3300"/>
-  <ax:ocxPr ax:name="_cy" ax:value="3300"/>
+  <ax:ocxPr ax:name="_cx" ax:value="4419"/>
+  <ax:ocxPr ax:name="_cy" ax:value="4207"/>
   <ax:ocxPr ax:name="Style" ax:value="11"/>
-  <ax:ocxPr ax:name="SubStyle" ax:value="0"/>
+  <ax:ocxPr ax:name="SubStyle" ax:value="-1"/>
   <ax:ocxPr ax:name="Validation" ax:value="2"/>
-  <ax:ocxPr ax:name="LineWeight" ax:value="3"/>
+  <ax:ocxPr ax:name="LineWeight" ax:value="1"/>
   <ax:ocxPr ax:name="Direction" ax:value="0"/>
   <ax:ocxPr ax:name="ShowData" ax:value="1"/>
-  <ax:ocxPr ax:name="Value" ax:value="PROOFREADOK"/>
+  <ax:ocxPr ax:name="Value" ax:value="KQR_Tag|Z019808491|3S20053064R|8|ZWSA0C|4506891869|00010|3S20053064||1004012|8|B2|19226|20251125||06891869|4506891869|"/>
   <ax:ocxPr ax:name="ForeColor" ax:value="0"/>
   <ax:ocxPr ax:name="BackColor" ax:value="16777215"/>
 </ax:ocx>
@@ -4433,15 +4460,15 @@
 
 <file path=xl/activeX/activeX204.xml><?xml version="1.0" encoding="utf-8"?>
 <ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{D9347033-9612-11D1-9D75-00C04FCC8CDC}" ax:persistence="persistPropertyBag">
-  <ax:ocxPr ax:name="_cx" ax:value="3300"/>
-  <ax:ocxPr ax:name="_cy" ax:value="3300"/>
+  <ax:ocxPr ax:name="_cx" ax:value="4842"/>
+  <ax:ocxPr ax:name="_cy" ax:value="4498"/>
   <ax:ocxPr ax:name="Style" ax:value="11"/>
   <ax:ocxPr ax:name="SubStyle" ax:value="-1"/>
   <ax:ocxPr ax:name="Validation" ax:value="2"/>
-  <ax:ocxPr ax:name="LineWeight" ax:value="3"/>
+  <ax:ocxPr ax:name="LineWeight" ax:value="1"/>
   <ax:ocxPr ax:name="Direction" ax:value="0"/>
   <ax:ocxPr ax:name="ShowData" ax:value="1"/>
-  <ax:ocxPr ax:name="Value" ax:value="CONFIRMPROOFREADNG"/>
+  <ax:ocxPr ax:name="Value" ax:value="3S200-53064"/>
   <ax:ocxPr ax:name="ForeColor" ax:value="0"/>
   <ax:ocxPr ax:name="BackColor" ax:value="16777215"/>
 </ax:ocx>
@@ -4449,15 +4476,15 @@
 
 <file path=xl/activeX/activeX205.xml><?xml version="1.0" encoding="utf-8"?>
 <ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{D9347033-9612-11D1-9D75-00C04FCC8CDC}" ax:persistence="persistPropertyBag">
-  <ax:ocxPr ax:name="_cx" ax:value="3300"/>
-  <ax:ocxPr ax:name="_cy" ax:value="3300"/>
+  <ax:ocxPr ax:name="_cx" ax:value="4815"/>
+  <ax:ocxPr ax:name="_cy" ax:value="4551"/>
   <ax:ocxPr ax:name="Style" ax:value="11"/>
-  <ax:ocxPr ax:name="SubStyle" ax:value="0"/>
+  <ax:ocxPr ax:name="SubStyle" ax:value="-1"/>
   <ax:ocxPr ax:name="Validation" ax:value="2"/>
   <ax:ocxPr ax:name="LineWeight" ax:value="1"/>
   <ax:ocxPr ax:name="Direction" ax:value="0"/>
   <ax:ocxPr ax:name="ShowData" ax:value="1"/>
-  <ax:ocxPr ax:name="Value" ax:value="C0101-G"/>
+  <ax:ocxPr ax:name="Value" ax:value="T1855-70642"/>
   <ax:ocxPr ax:name="ForeColor" ax:value="0"/>
   <ax:ocxPr ax:name="BackColor" ax:value="16777215"/>
 </ax:ocx>
@@ -4465,10 +4492,10 @@
 
 <file path=xl/activeX/activeX206.xml><?xml version="1.0" encoding="utf-8"?>
 <ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{D9347033-9612-11D1-9D75-00C04FCC8CDC}" ax:persistence="persistPropertyBag">
-  <ax:ocxPr ax:name="_cx" ax:value="3300"/>
-  <ax:ocxPr ax:name="_cy" ax:value="3300"/>
+  <ax:ocxPr ax:name="_cx" ax:value="3307"/>
+  <ax:ocxPr ax:name="_cy" ax:value="3334"/>
   <ax:ocxPr ax:name="Style" ax:value="11"/>
-  <ax:ocxPr ax:name="SubStyle" ax:value="-1"/>
+  <ax:ocxPr ax:name="SubStyle" ax:value="0"/>
   <ax:ocxPr ax:name="Validation" ax:value="2"/>
   <ax:ocxPr ax:name="LineWeight" ax:value="1"/>
   <ax:ocxPr ax:name="Direction" ax:value="0"/>
@@ -4481,15 +4508,15 @@
 
 <file path=xl/activeX/activeX207.xml><?xml version="1.0" encoding="utf-8"?>
 <ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{D9347033-9612-11D1-9D75-00C04FCC8CDC}" ax:persistence="persistPropertyBag">
-  <ax:ocxPr ax:name="_cx" ax:value="3300"/>
-  <ax:ocxPr ax:name="_cy" ax:value="3300"/>
+  <ax:ocxPr ax:name="_cx" ax:value="3307"/>
+  <ax:ocxPr ax:name="_cy" ax:value="3334"/>
   <ax:ocxPr ax:name="Style" ax:value="11"/>
   <ax:ocxPr ax:name="SubStyle" ax:value="-1"/>
   <ax:ocxPr ax:name="Validation" ax:value="2"/>
   <ax:ocxPr ax:name="LineWeight" ax:value="1"/>
   <ax:ocxPr ax:name="Direction" ax:value="0"/>
   <ax:ocxPr ax:name="ShowData" ax:value="1"/>
-  <ax:ocxPr ax:name="Value" ax:value="C0101-W"/>
+  <ax:ocxPr ax:name="Value" ax:value="EWU"/>
   <ax:ocxPr ax:name="ForeColor" ax:value="0"/>
   <ax:ocxPr ax:name="BackColor" ax:value="16777215"/>
 </ax:ocx>
@@ -4497,15 +4524,15 @@
 
 <file path=xl/activeX/activeX208.xml><?xml version="1.0" encoding="utf-8"?>
 <ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{D9347033-9612-11D1-9D75-00C04FCC8CDC}" ax:persistence="persistPropertyBag">
-  <ax:ocxPr ax:name="_cx" ax:value="3300"/>
-  <ax:ocxPr ax:name="_cy" ax:value="3300"/>
+  <ax:ocxPr ax:name="_cx" ax:value="4419"/>
+  <ax:ocxPr ax:name="_cy" ax:value="4260"/>
   <ax:ocxPr ax:name="Style" ax:value="11"/>
   <ax:ocxPr ax:name="SubStyle" ax:value="-1"/>
   <ax:ocxPr ax:name="Validation" ax:value="2"/>
   <ax:ocxPr ax:name="LineWeight" ax:value="1"/>
   <ax:ocxPr ax:name="Direction" ax:value="0"/>
   <ax:ocxPr ax:name="ShowData" ax:value="1"/>
-  <ax:ocxPr ax:name="Value" ax:value="C0101-G"/>
+  <ax:ocxPr ax:name="Value" ax:value="28T18557064284026244001601- -  ｶﾝﾄ-ｳ-ｻﾝ0000040ML   0000040                      20251126            "/>
   <ax:ocxPr ax:name="ForeColor" ax:value="0"/>
   <ax:ocxPr ax:name="BackColor" ax:value="16777215"/>
 </ax:ocx>
@@ -4513,15 +4540,15 @@
 
 <file path=xl/activeX/activeX209.xml><?xml version="1.0" encoding="utf-8"?>
 <ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{D9347033-9612-11D1-9D75-00C04FCC8CDC}" ax:persistence="persistPropertyBag">
-  <ax:ocxPr ax:name="_cx" ax:value="3300"/>
-  <ax:ocxPr ax:name="_cy" ax:value="3300"/>
+  <ax:ocxPr ax:name="_cx" ax:value="4842"/>
+  <ax:ocxPr ax:name="_cy" ax:value="4471"/>
   <ax:ocxPr ax:name="Style" ax:value="11"/>
   <ax:ocxPr ax:name="SubStyle" ax:value="0"/>
   <ax:ocxPr ax:name="Validation" ax:value="2"/>
   <ax:ocxPr ax:name="LineWeight" ax:value="1"/>
   <ax:ocxPr ax:name="Direction" ax:value="0"/>
   <ax:ocxPr ax:name="ShowData" ax:value="1"/>
-  <ax:ocxPr ax:name="Value" ax:value="C0101-Y"/>
+  <ax:ocxPr ax:name="Value" ax:value="T1855-70743"/>
   <ax:ocxPr ax:name="ForeColor" ax:value="0"/>
   <ax:ocxPr ax:name="BackColor" ax:value="16777215"/>
 </ax:ocx>
@@ -4545,15 +4572,15 @@
 
 <file path=xl/activeX/activeX210.xml><?xml version="1.0" encoding="utf-8"?>
 <ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{D9347033-9612-11D1-9D75-00C04FCC8CDC}" ax:persistence="persistPropertyBag">
-  <ax:ocxPr ax:name="_cx" ax:value="3300"/>
-  <ax:ocxPr ax:name="_cy" ax:value="3300"/>
+  <ax:ocxPr ax:name="_cx" ax:value="4419"/>
+  <ax:ocxPr ax:name="_cy" ax:value="4128"/>
   <ax:ocxPr ax:name="Style" ax:value="11"/>
   <ax:ocxPr ax:name="SubStyle" ax:value="0"/>
   <ax:ocxPr ax:name="Validation" ax:value="2"/>
   <ax:ocxPr ax:name="LineWeight" ax:value="1"/>
   <ax:ocxPr ax:name="Direction" ax:value="0"/>
   <ax:ocxPr ax:name="ShowData" ax:value="1"/>
-  <ax:ocxPr ax:name="Value" ax:value="C0101-W"/>
+  <ax:ocxPr ax:name="Value" ax:value="28T18557074384026277001601- -  ｶﾝﾄ-ｳ-ｻﾝ0000040ML   0000040                      20251126            "/>
   <ax:ocxPr ax:name="ForeColor" ax:value="0"/>
   <ax:ocxPr ax:name="BackColor" ax:value="16777215"/>
 </ax:ocx>
@@ -4566,10 +4593,10 @@
   <ax:ocxPr ax:name="Style" ax:value="11"/>
   <ax:ocxPr ax:name="SubStyle" ax:value="-1"/>
   <ax:ocxPr ax:name="Validation" ax:value="2"/>
-  <ax:ocxPr ax:name="LineWeight" ax:value="1"/>
+  <ax:ocxPr ax:name="LineWeight" ax:value="3"/>
   <ax:ocxPr ax:name="Direction" ax:value="0"/>
   <ax:ocxPr ax:name="ShowData" ax:value="1"/>
-  <ax:ocxPr ax:name="Value" ax:value="C0105-G"/>
+  <ax:ocxPr ax:name="Value" ax:value="PROOFREAD-OK"/>
   <ax:ocxPr ax:name="ForeColor" ax:value="0"/>
   <ax:ocxPr ax:name="BackColor" ax:value="16777215"/>
 </ax:ocx>
@@ -4582,10 +4609,10 @@
   <ax:ocxPr ax:name="Style" ax:value="11"/>
   <ax:ocxPr ax:name="SubStyle" ax:value="0"/>
   <ax:ocxPr ax:name="Validation" ax:value="2"/>
-  <ax:ocxPr ax:name="LineWeight" ax:value="1"/>
+  <ax:ocxPr ax:name="LineWeight" ax:value="3"/>
   <ax:ocxPr ax:name="Direction" ax:value="0"/>
   <ax:ocxPr ax:name="ShowData" ax:value="1"/>
-  <ax:ocxPr ax:name="Value" ax:value="C0105-Y"/>
+  <ax:ocxPr ax:name="Value" ax:value="PROOFREAD-NG"/>
   <ax:ocxPr ax:name="ForeColor" ax:value="0"/>
   <ax:ocxPr ax:name="BackColor" ax:value="16777215"/>
 </ax:ocx>
@@ -4598,10 +4625,10 @@
   <ax:ocxPr ax:name="Style" ax:value="11"/>
   <ax:ocxPr ax:name="SubStyle" ax:value="0"/>
   <ax:ocxPr ax:name="Validation" ax:value="2"/>
-  <ax:ocxPr ax:name="LineWeight" ax:value="1"/>
+  <ax:ocxPr ax:name="LineWeight" ax:value="3"/>
   <ax:ocxPr ax:name="Direction" ax:value="0"/>
   <ax:ocxPr ax:name="ShowData" ax:value="1"/>
-  <ax:ocxPr ax:name="Value" ax:value="C0105-W"/>
+  <ax:ocxPr ax:name="Value" ax:value="PROOFREADOK"/>
   <ax:ocxPr ax:name="ForeColor" ax:value="0"/>
   <ax:ocxPr ax:name="BackColor" ax:value="16777215"/>
 </ax:ocx>
@@ -4614,10 +4641,10 @@
   <ax:ocxPr ax:name="Style" ax:value="11"/>
   <ax:ocxPr ax:name="SubStyle" ax:value="-1"/>
   <ax:ocxPr ax:name="Validation" ax:value="2"/>
-  <ax:ocxPr ax:name="LineWeight" ax:value="1"/>
+  <ax:ocxPr ax:name="LineWeight" ax:value="3"/>
   <ax:ocxPr ax:name="Direction" ax:value="0"/>
   <ax:ocxPr ax:name="ShowData" ax:value="1"/>
-  <ax:ocxPr ax:name="Value" ax:value="C0105-G"/>
+  <ax:ocxPr ax:name="Value" ax:value="CONFIRMPROOFREADNG"/>
   <ax:ocxPr ax:name="ForeColor" ax:value="0"/>
   <ax:ocxPr ax:name="BackColor" ax:value="16777215"/>
 </ax:ocx>
@@ -4633,7 +4660,7 @@
   <ax:ocxPr ax:name="LineWeight" ax:value="1"/>
   <ax:ocxPr ax:name="Direction" ax:value="0"/>
   <ax:ocxPr ax:name="ShowData" ax:value="1"/>
-  <ax:ocxPr ax:name="Value" ax:value="C0105-Y"/>
+  <ax:ocxPr ax:name="Value" ax:value="C0101-G"/>
   <ax:ocxPr ax:name="ForeColor" ax:value="0"/>
   <ax:ocxPr ax:name="BackColor" ax:value="16777215"/>
 </ax:ocx>
@@ -4644,12 +4671,12 @@
   <ax:ocxPr ax:name="_cx" ax:value="3300"/>
   <ax:ocxPr ax:name="_cy" ax:value="3300"/>
   <ax:ocxPr ax:name="Style" ax:value="11"/>
-  <ax:ocxPr ax:name="SubStyle" ax:value="0"/>
+  <ax:ocxPr ax:name="SubStyle" ax:value="-1"/>
   <ax:ocxPr ax:name="Validation" ax:value="2"/>
   <ax:ocxPr ax:name="LineWeight" ax:value="1"/>
   <ax:ocxPr ax:name="Direction" ax:value="0"/>
   <ax:ocxPr ax:name="ShowData" ax:value="1"/>
-  <ax:ocxPr ax:name="Value" ax:value="C0105-W"/>
+  <ax:ocxPr ax:name="Value" ax:value="C0101-Y"/>
   <ax:ocxPr ax:name="ForeColor" ax:value="0"/>
   <ax:ocxPr ax:name="BackColor" ax:value="16777215"/>
 </ax:ocx>
@@ -4660,12 +4687,12 @@
   <ax:ocxPr ax:name="_cx" ax:value="3300"/>
   <ax:ocxPr ax:name="_cy" ax:value="3300"/>
   <ax:ocxPr ax:name="Style" ax:value="11"/>
-  <ax:ocxPr ax:name="SubStyle" ax:value="0"/>
+  <ax:ocxPr ax:name="SubStyle" ax:value="-1"/>
   <ax:ocxPr ax:name="Validation" ax:value="2"/>
   <ax:ocxPr ax:name="LineWeight" ax:value="1"/>
   <ax:ocxPr ax:name="Direction" ax:value="0"/>
   <ax:ocxPr ax:name="ShowData" ax:value="1"/>
-  <ax:ocxPr ax:name="Value" ax:value="C0101-G"/>
+  <ax:ocxPr ax:name="Value" ax:value="C0101-W"/>
   <ax:ocxPr ax:name="ForeColor" ax:value="0"/>
   <ax:ocxPr ax:name="BackColor" ax:value="16777215"/>
 </ax:ocx>
@@ -4681,7 +4708,7 @@
   <ax:ocxPr ax:name="LineWeight" ax:value="1"/>
   <ax:ocxPr ax:name="Direction" ax:value="0"/>
   <ax:ocxPr ax:name="ShowData" ax:value="1"/>
-  <ax:ocxPr ax:name="Value" ax:value="C0101-Y"/>
+  <ax:ocxPr ax:name="Value" ax:value="C0101-G"/>
   <ax:ocxPr ax:name="ForeColor" ax:value="0"/>
   <ax:ocxPr ax:name="BackColor" ax:value="16777215"/>
 </ax:ocx>
@@ -4692,12 +4719,12 @@
   <ax:ocxPr ax:name="_cx" ax:value="3300"/>
   <ax:ocxPr ax:name="_cy" ax:value="3300"/>
   <ax:ocxPr ax:name="Style" ax:value="11"/>
-  <ax:ocxPr ax:name="SubStyle" ax:value="-1"/>
+  <ax:ocxPr ax:name="SubStyle" ax:value="0"/>
   <ax:ocxPr ax:name="Validation" ax:value="2"/>
   <ax:ocxPr ax:name="LineWeight" ax:value="1"/>
   <ax:ocxPr ax:name="Direction" ax:value="0"/>
   <ax:ocxPr ax:name="ShowData" ax:value="1"/>
-  <ax:ocxPr ax:name="Value" ax:value="C0101-W"/>
+  <ax:ocxPr ax:name="Value" ax:value="C0101-Y"/>
   <ax:ocxPr ax:name="ForeColor" ax:value="0"/>
   <ax:ocxPr ax:name="BackColor" ax:value="16777215"/>
 </ax:ocx>
@@ -4729,7 +4756,7 @@
   <ax:ocxPr ax:name="LineWeight" ax:value="1"/>
   <ax:ocxPr ax:name="Direction" ax:value="0"/>
   <ax:ocxPr ax:name="ShowData" ax:value="1"/>
-  <ax:ocxPr ax:name="Value" ax:value="C0105-G"/>
+  <ax:ocxPr ax:name="Value" ax:value="C0101-W"/>
   <ax:ocxPr ax:name="ForeColor" ax:value="0"/>
   <ax:ocxPr ax:name="BackColor" ax:value="16777215"/>
 </ax:ocx>
@@ -4745,7 +4772,7 @@
   <ax:ocxPr ax:name="LineWeight" ax:value="1"/>
   <ax:ocxPr ax:name="Direction" ax:value="0"/>
   <ax:ocxPr ax:name="ShowData" ax:value="1"/>
-  <ax:ocxPr ax:name="Value" ax:value="C0105-Y"/>
+  <ax:ocxPr ax:name="Value" ax:value="C0105-G"/>
   <ax:ocxPr ax:name="ForeColor" ax:value="0"/>
   <ax:ocxPr ax:name="BackColor" ax:value="16777215"/>
 </ax:ocx>
@@ -4756,12 +4783,12 @@
   <ax:ocxPr ax:name="_cx" ax:value="3300"/>
   <ax:ocxPr ax:name="_cy" ax:value="3300"/>
   <ax:ocxPr ax:name="Style" ax:value="11"/>
-  <ax:ocxPr ax:name="SubStyle" ax:value="-1"/>
+  <ax:ocxPr ax:name="SubStyle" ax:value="0"/>
   <ax:ocxPr ax:name="Validation" ax:value="2"/>
   <ax:ocxPr ax:name="LineWeight" ax:value="1"/>
   <ax:ocxPr ax:name="Direction" ax:value="0"/>
   <ax:ocxPr ax:name="ShowData" ax:value="1"/>
-  <ax:ocxPr ax:name="Value" ax:value="C0105-W"/>
+  <ax:ocxPr ax:name="Value" ax:value="C0105-Y"/>
   <ax:ocxPr ax:name="ForeColor" ax:value="0"/>
   <ax:ocxPr ax:name="BackColor" ax:value="16777215"/>
 </ax:ocx>
@@ -4777,7 +4804,7 @@
   <ax:ocxPr ax:name="LineWeight" ax:value="1"/>
   <ax:ocxPr ax:name="Direction" ax:value="0"/>
   <ax:ocxPr ax:name="ShowData" ax:value="1"/>
-  <ax:ocxPr ax:name="Value" ax:value="C0105-1W"/>
+  <ax:ocxPr ax:name="Value" ax:value="C0105-W"/>
   <ax:ocxPr ax:name="ForeColor" ax:value="0"/>
   <ax:ocxPr ax:name="BackColor" ax:value="16777215"/>
 </ax:ocx>
@@ -4788,12 +4815,12 @@
   <ax:ocxPr ax:name="_cx" ax:value="3300"/>
   <ax:ocxPr ax:name="_cy" ax:value="3300"/>
   <ax:ocxPr ax:name="Style" ax:value="11"/>
-  <ax:ocxPr ax:name="SubStyle" ax:value="0"/>
+  <ax:ocxPr ax:name="SubStyle" ax:value="-1"/>
   <ax:ocxPr ax:name="Validation" ax:value="2"/>
   <ax:ocxPr ax:name="LineWeight" ax:value="1"/>
   <ax:ocxPr ax:name="Direction" ax:value="0"/>
   <ax:ocxPr ax:name="ShowData" ax:value="1"/>
-  <ax:ocxPr ax:name="Value" ax:value="C0105-1W"/>
+  <ax:ocxPr ax:name="Value" ax:value="C0105-G"/>
   <ax:ocxPr ax:name="ForeColor" ax:value="0"/>
   <ax:ocxPr ax:name="BackColor" ax:value="16777215"/>
 </ax:ocx>
@@ -4809,7 +4836,7 @@
   <ax:ocxPr ax:name="LineWeight" ax:value="1"/>
   <ax:ocxPr ax:name="Direction" ax:value="0"/>
   <ax:ocxPr ax:name="ShowData" ax:value="1"/>
-  <ax:ocxPr ax:name="Value" ax:value="C0105-1W"/>
+  <ax:ocxPr ax:name="Value" ax:value="C0105-Y"/>
   <ax:ocxPr ax:name="ForeColor" ax:value="0"/>
   <ax:ocxPr ax:name="BackColor" ax:value="16777215"/>
 </ax:ocx>
@@ -4825,7 +4852,55 @@
   <ax:ocxPr ax:name="LineWeight" ax:value="1"/>
   <ax:ocxPr ax:name="Direction" ax:value="0"/>
   <ax:ocxPr ax:name="ShowData" ax:value="1"/>
-  <ax:ocxPr ax:name="Value" ax:value="7d5d465dcd0380"/>
+  <ax:ocxPr ax:name="Value" ax:value="C0105-W"/>
+  <ax:ocxPr ax:name="ForeColor" ax:value="0"/>
+  <ax:ocxPr ax:name="BackColor" ax:value="16777215"/>
+</ax:ocx>
+</file>
+
+<file path=xl/activeX/activeX227.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{D9347033-9612-11D1-9D75-00C04FCC8CDC}" ax:persistence="persistPropertyBag">
+  <ax:ocxPr ax:name="_cx" ax:value="3300"/>
+  <ax:ocxPr ax:name="_cy" ax:value="3300"/>
+  <ax:ocxPr ax:name="Style" ax:value="11"/>
+  <ax:ocxPr ax:name="SubStyle" ax:value="0"/>
+  <ax:ocxPr ax:name="Validation" ax:value="2"/>
+  <ax:ocxPr ax:name="LineWeight" ax:value="1"/>
+  <ax:ocxPr ax:name="Direction" ax:value="0"/>
+  <ax:ocxPr ax:name="ShowData" ax:value="1"/>
+  <ax:ocxPr ax:name="Value" ax:value="C0101-G"/>
+  <ax:ocxPr ax:name="ForeColor" ax:value="0"/>
+  <ax:ocxPr ax:name="BackColor" ax:value="16777215"/>
+</ax:ocx>
+</file>
+
+<file path=xl/activeX/activeX228.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{D9347033-9612-11D1-9D75-00C04FCC8CDC}" ax:persistence="persistPropertyBag">
+  <ax:ocxPr ax:name="_cx" ax:value="3300"/>
+  <ax:ocxPr ax:name="_cy" ax:value="3300"/>
+  <ax:ocxPr ax:name="Style" ax:value="11"/>
+  <ax:ocxPr ax:name="SubStyle" ax:value="-1"/>
+  <ax:ocxPr ax:name="Validation" ax:value="2"/>
+  <ax:ocxPr ax:name="LineWeight" ax:value="1"/>
+  <ax:ocxPr ax:name="Direction" ax:value="0"/>
+  <ax:ocxPr ax:name="ShowData" ax:value="1"/>
+  <ax:ocxPr ax:name="Value" ax:value="C0101-Y"/>
+  <ax:ocxPr ax:name="ForeColor" ax:value="0"/>
+  <ax:ocxPr ax:name="BackColor" ax:value="16777215"/>
+</ax:ocx>
+</file>
+
+<file path=xl/activeX/activeX229.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{D9347033-9612-11D1-9D75-00C04FCC8CDC}" ax:persistence="persistPropertyBag">
+  <ax:ocxPr ax:name="_cx" ax:value="3300"/>
+  <ax:ocxPr ax:name="_cy" ax:value="3300"/>
+  <ax:ocxPr ax:name="Style" ax:value="11"/>
+  <ax:ocxPr ax:name="SubStyle" ax:value="-1"/>
+  <ax:ocxPr ax:name="Validation" ax:value="2"/>
+  <ax:ocxPr ax:name="LineWeight" ax:value="1"/>
+  <ax:ocxPr ax:name="Direction" ax:value="0"/>
+  <ax:ocxPr ax:name="ShowData" ax:value="1"/>
+  <ax:ocxPr ax:name="Value" ax:value="C0101-W"/>
   <ax:ocxPr ax:name="ForeColor" ax:value="0"/>
   <ax:ocxPr ax:name="BackColor" ax:value="16777215"/>
 </ax:ocx>
@@ -4842,6 +4917,118 @@
   <ax:ocxPr ax:name="Direction" ax:value="0"/>
   <ax:ocxPr ax:name="ShowData" ax:value="1"/>
   <ax:ocxPr ax:name="Value" ax:value="1J500-17321"/>
+  <ax:ocxPr ax:name="ForeColor" ax:value="0"/>
+  <ax:ocxPr ax:name="BackColor" ax:value="16777215"/>
+</ax:ocx>
+</file>
+
+<file path=xl/activeX/activeX230.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{D9347033-9612-11D1-9D75-00C04FCC8CDC}" ax:persistence="persistPropertyBag">
+  <ax:ocxPr ax:name="_cx" ax:value="3300"/>
+  <ax:ocxPr ax:name="_cy" ax:value="3300"/>
+  <ax:ocxPr ax:name="Style" ax:value="11"/>
+  <ax:ocxPr ax:name="SubStyle" ax:value="0"/>
+  <ax:ocxPr ax:name="Validation" ax:value="2"/>
+  <ax:ocxPr ax:name="LineWeight" ax:value="1"/>
+  <ax:ocxPr ax:name="Direction" ax:value="0"/>
+  <ax:ocxPr ax:name="ShowData" ax:value="1"/>
+  <ax:ocxPr ax:name="Value" ax:value="C0105-G"/>
+  <ax:ocxPr ax:name="ForeColor" ax:value="0"/>
+  <ax:ocxPr ax:name="BackColor" ax:value="16777215"/>
+</ax:ocx>
+</file>
+
+<file path=xl/activeX/activeX231.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{D9347033-9612-11D1-9D75-00C04FCC8CDC}" ax:persistence="persistPropertyBag">
+  <ax:ocxPr ax:name="_cx" ax:value="3300"/>
+  <ax:ocxPr ax:name="_cy" ax:value="3300"/>
+  <ax:ocxPr ax:name="Style" ax:value="11"/>
+  <ax:ocxPr ax:name="SubStyle" ax:value="-1"/>
+  <ax:ocxPr ax:name="Validation" ax:value="2"/>
+  <ax:ocxPr ax:name="LineWeight" ax:value="1"/>
+  <ax:ocxPr ax:name="Direction" ax:value="0"/>
+  <ax:ocxPr ax:name="ShowData" ax:value="1"/>
+  <ax:ocxPr ax:name="Value" ax:value="C0105-Y"/>
+  <ax:ocxPr ax:name="ForeColor" ax:value="0"/>
+  <ax:ocxPr ax:name="BackColor" ax:value="16777215"/>
+</ax:ocx>
+</file>
+
+<file path=xl/activeX/activeX232.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{D9347033-9612-11D1-9D75-00C04FCC8CDC}" ax:persistence="persistPropertyBag">
+  <ax:ocxPr ax:name="_cx" ax:value="3300"/>
+  <ax:ocxPr ax:name="_cy" ax:value="3300"/>
+  <ax:ocxPr ax:name="Style" ax:value="11"/>
+  <ax:ocxPr ax:name="SubStyle" ax:value="-1"/>
+  <ax:ocxPr ax:name="Validation" ax:value="2"/>
+  <ax:ocxPr ax:name="LineWeight" ax:value="1"/>
+  <ax:ocxPr ax:name="Direction" ax:value="0"/>
+  <ax:ocxPr ax:name="ShowData" ax:value="1"/>
+  <ax:ocxPr ax:name="Value" ax:value="C0105-W"/>
+  <ax:ocxPr ax:name="ForeColor" ax:value="0"/>
+  <ax:ocxPr ax:name="BackColor" ax:value="16777215"/>
+</ax:ocx>
+</file>
+
+<file path=xl/activeX/activeX233.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{D9347033-9612-11D1-9D75-00C04FCC8CDC}" ax:persistence="persistPropertyBag">
+  <ax:ocxPr ax:name="_cx" ax:value="3300"/>
+  <ax:ocxPr ax:name="_cy" ax:value="3300"/>
+  <ax:ocxPr ax:name="Style" ax:value="11"/>
+  <ax:ocxPr ax:name="SubStyle" ax:value="0"/>
+  <ax:ocxPr ax:name="Validation" ax:value="2"/>
+  <ax:ocxPr ax:name="LineWeight" ax:value="1"/>
+  <ax:ocxPr ax:name="Direction" ax:value="0"/>
+  <ax:ocxPr ax:name="ShowData" ax:value="1"/>
+  <ax:ocxPr ax:name="Value" ax:value="C0105-1W"/>
+  <ax:ocxPr ax:name="ForeColor" ax:value="0"/>
+  <ax:ocxPr ax:name="BackColor" ax:value="16777215"/>
+</ax:ocx>
+</file>
+
+<file path=xl/activeX/activeX234.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{D9347033-9612-11D1-9D75-00C04FCC8CDC}" ax:persistence="persistPropertyBag">
+  <ax:ocxPr ax:name="_cx" ax:value="3300"/>
+  <ax:ocxPr ax:name="_cy" ax:value="3300"/>
+  <ax:ocxPr ax:name="Style" ax:value="11"/>
+  <ax:ocxPr ax:name="SubStyle" ax:value="0"/>
+  <ax:ocxPr ax:name="Validation" ax:value="2"/>
+  <ax:ocxPr ax:name="LineWeight" ax:value="1"/>
+  <ax:ocxPr ax:name="Direction" ax:value="0"/>
+  <ax:ocxPr ax:name="ShowData" ax:value="1"/>
+  <ax:ocxPr ax:name="Value" ax:value="C0105-1W"/>
+  <ax:ocxPr ax:name="ForeColor" ax:value="0"/>
+  <ax:ocxPr ax:name="BackColor" ax:value="16777215"/>
+</ax:ocx>
+</file>
+
+<file path=xl/activeX/activeX235.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{D9347033-9612-11D1-9D75-00C04FCC8CDC}" ax:persistence="persistPropertyBag">
+  <ax:ocxPr ax:name="_cx" ax:value="3300"/>
+  <ax:ocxPr ax:name="_cy" ax:value="3300"/>
+  <ax:ocxPr ax:name="Style" ax:value="11"/>
+  <ax:ocxPr ax:name="SubStyle" ax:value="0"/>
+  <ax:ocxPr ax:name="Validation" ax:value="2"/>
+  <ax:ocxPr ax:name="LineWeight" ax:value="1"/>
+  <ax:ocxPr ax:name="Direction" ax:value="0"/>
+  <ax:ocxPr ax:name="ShowData" ax:value="1"/>
+  <ax:ocxPr ax:name="Value" ax:value="C0105-1W"/>
+  <ax:ocxPr ax:name="ForeColor" ax:value="0"/>
+  <ax:ocxPr ax:name="BackColor" ax:value="16777215"/>
+</ax:ocx>
+</file>
+
+<file path=xl/activeX/activeX236.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{D9347033-9612-11D1-9D75-00C04FCC8CDC}" ax:persistence="persistPropertyBag">
+  <ax:ocxPr ax:name="_cx" ax:value="3300"/>
+  <ax:ocxPr ax:name="_cy" ax:value="3300"/>
+  <ax:ocxPr ax:name="Style" ax:value="11"/>
+  <ax:ocxPr ax:name="SubStyle" ax:value="0"/>
+  <ax:ocxPr ax:name="Validation" ax:value="2"/>
+  <ax:ocxPr ax:name="LineWeight" ax:value="1"/>
+  <ax:ocxPr ax:name="Direction" ax:value="0"/>
+  <ax:ocxPr ax:name="ShowData" ax:value="1"/>
+  <ax:ocxPr ax:name="Value" ax:value="7d5d465dcd0380"/>
   <ax:ocxPr ax:name="ForeColor" ax:value="0"/>
   <ax:ocxPr ax:name="BackColor" ax:value="16777215"/>
 </ax:ocx>
@@ -14962,10 +15149,10 @@
           <xdr:rowOff>38100</xdr:rowOff>
         </xdr:from>
         <xdr:to>
-          <xdr:col>11</xdr:col>
-          <xdr:colOff>438150</xdr:colOff>
-          <xdr:row>24</xdr:row>
-          <xdr:rowOff>114300</xdr:rowOff>
+          <xdr:col>10</xdr:col>
+          <xdr:colOff>571500</xdr:colOff>
+          <xdr:row>22</xdr:row>
+          <xdr:rowOff>28575</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -15021,9 +15208,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>4</xdr:col>
-          <xdr:colOff>552450</xdr:colOff>
-          <xdr:row>24</xdr:row>
-          <xdr:rowOff>114300</xdr:rowOff>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>22</xdr:row>
+          <xdr:rowOff>28575</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -15078,10 +15265,10 @@
           <xdr:rowOff>38100</xdr:rowOff>
         </xdr:from>
         <xdr:to>
-          <xdr:col>11</xdr:col>
-          <xdr:colOff>381000</xdr:colOff>
-          <xdr:row>45</xdr:row>
-          <xdr:rowOff>114300</xdr:rowOff>
+          <xdr:col>10</xdr:col>
+          <xdr:colOff>514350</xdr:colOff>
+          <xdr:row>43</xdr:row>
+          <xdr:rowOff>28575</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -15137,9 +15324,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>4</xdr:col>
-          <xdr:colOff>552450</xdr:colOff>
-          <xdr:row>45</xdr:row>
-          <xdr:rowOff>114300</xdr:rowOff>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>43</xdr:row>
+          <xdr:rowOff>28575</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -15197,7 +15384,7 @@
           <xdr:col>4</xdr:col>
           <xdr:colOff>409575</xdr:colOff>
           <xdr:row>10</xdr:row>
-          <xdr:rowOff>28575</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -15426,9 +15613,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>4</xdr:col>
-          <xdr:colOff>552450</xdr:colOff>
-          <xdr:row>24</xdr:row>
-          <xdr:rowOff>114300</xdr:rowOff>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>22</xdr:row>
+          <xdr:rowOff>28575</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -15486,7 +15673,7 @@
           <xdr:col>4</xdr:col>
           <xdr:colOff>409575</xdr:colOff>
           <xdr:row>10</xdr:row>
-          <xdr:rowOff>28575</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -15622,7 +15809,7 @@
           <xdr:col>4</xdr:col>
           <xdr:colOff>552450</xdr:colOff>
           <xdr:row>23</xdr:row>
-          <xdr:rowOff>114299</xdr:rowOff>
+          <xdr:rowOff>114300</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -15727,13 +15914,13 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>8</xdr:col>
-          <xdr:colOff>54769</xdr:colOff>
+          <xdr:colOff>57150</xdr:colOff>
           <xdr:row>3</xdr:row>
           <xdr:rowOff>28575</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>9</xdr:col>
-          <xdr:colOff>564356</xdr:colOff>
+          <xdr:colOff>561975</xdr:colOff>
           <xdr:row>10</xdr:row>
           <xdr:rowOff>28575</xdr:rowOff>
         </xdr:to>
@@ -15790,7 +15977,7 @@
           <xdr:col>10</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
           <xdr:row>23</xdr:row>
-          <xdr:rowOff>11905</xdr:rowOff>
+          <xdr:rowOff>9525</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -15845,7 +16032,7 @@
           <xdr:col>4</xdr:col>
           <xdr:colOff>552450</xdr:colOff>
           <xdr:row>39</xdr:row>
-          <xdr:rowOff>114299</xdr:rowOff>
+          <xdr:rowOff>114300</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -15900,7 +16087,7 @@
           <xdr:col>10</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
           <xdr:row>39</xdr:row>
-          <xdr:rowOff>9524</xdr:rowOff>
+          <xdr:rowOff>9525</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -15946,6 +16133,544 @@
 </file>
 
 <file path=xl/drawings/drawing26.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>664368</xdr:colOff>
+          <xdr:row>13</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>6</xdr:col>
+          <xdr:colOff>345281</xdr:colOff>
+          <xdr:row>21</xdr:row>
+          <xdr:rowOff>128588</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="55297" name="BarCodeCtrl2" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s55297"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-1400-000002880000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:noFill/>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>2</xdr:col>
+          <xdr:colOff>590550</xdr:colOff>
+          <xdr:row>3</xdr:row>
+          <xdr:rowOff>28575</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>409575</xdr:colOff>
+          <xdr:row>10</xdr:row>
+          <xdr:rowOff>28575</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="55298" name="BarCodeCtrl5" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s55298"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:noFill/>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>8</xdr:col>
+          <xdr:colOff>57150</xdr:colOff>
+          <xdr:row>3</xdr:row>
+          <xdr:rowOff>28575</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>9</xdr:col>
+          <xdr:colOff>561975</xdr:colOff>
+          <xdr:row>10</xdr:row>
+          <xdr:rowOff>28575</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="55299" name="BarCodeCtrl3" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s55299"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:noFill/>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>12</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>13</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>14</xdr:col>
+          <xdr:colOff>219075</xdr:colOff>
+          <xdr:row>21</xdr:row>
+          <xdr:rowOff>23813</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="55300" name="BarCodeCtrl1" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s55300"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:noFill/>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>2</xdr:col>
+          <xdr:colOff>119063</xdr:colOff>
+          <xdr:row>29</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>490538</xdr:colOff>
+          <xdr:row>37</xdr:row>
+          <xdr:rowOff>100013</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="55301" name="BarCodeCtrl4" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s55301"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:noFill/>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>8</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>28</xdr:row>
+          <xdr:rowOff>290513</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>10</xdr:col>
+          <xdr:colOff>219075</xdr:colOff>
+          <xdr:row>36</xdr:row>
+          <xdr:rowOff>142876</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="55302" name="BarCodeCtrl6" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s55302"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:noFill/>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:oneCellAnchor>
+        <xdr:from>
+          <xdr:col>2</xdr:col>
+          <xdr:colOff>119063</xdr:colOff>
+          <xdr:row>43</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:ext cx="1752600" cy="1576388"/>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="55303" name="BarCodeCtrl7" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s55303"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:noFill/>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:oneCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:oneCellAnchor>
+        <xdr:from>
+          <xdr:col>8</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>42</xdr:row>
+          <xdr:rowOff>290513</xdr:rowOff>
+        </xdr:from>
+        <xdr:ext cx="1600200" cy="1471613"/>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="55304" name="BarCodeCtrl8" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s55304"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:noFill/>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:oneCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:oneCellAnchor>
+        <xdr:from>
+          <xdr:col>2</xdr:col>
+          <xdr:colOff>119063</xdr:colOff>
+          <xdr:row>57</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:ext cx="1752600" cy="1576388"/>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="55305" name="BarCodeCtrl9" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s55305"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:noFill/>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:oneCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:oneCellAnchor>
+        <xdr:from>
+          <xdr:col>8</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>56</xdr:row>
+          <xdr:rowOff>290513</xdr:rowOff>
+        </xdr:from>
+        <xdr:ext cx="1600200" cy="1471613"/>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="55306" name="BarCodeCtrl10" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s55306"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:noFill/>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:oneCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing27.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
@@ -16282,7 +17007,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing28.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -19495,7 +20220,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing29.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
@@ -21969,39 +22694,39 @@
     </row>
     <row r="9" spans="2:11" ht="14.25" thickBot="1"/>
     <row r="10" spans="2:11">
-      <c r="B10" s="49" t="s">
+      <c r="B10" s="51" t="s">
         <v>81</v>
       </c>
-      <c r="C10" s="50"/>
-      <c r="D10" s="50"/>
-      <c r="E10" s="50"/>
-      <c r="F10" s="50"/>
-      <c r="G10" s="50"/>
-      <c r="H10" s="50"/>
-      <c r="I10" s="50"/>
-      <c r="J10" s="51"/>
+      <c r="C10" s="52"/>
+      <c r="D10" s="52"/>
+      <c r="E10" s="52"/>
+      <c r="F10" s="52"/>
+      <c r="G10" s="52"/>
+      <c r="H10" s="52"/>
+      <c r="I10" s="52"/>
+      <c r="J10" s="53"/>
     </row>
     <row r="11" spans="2:11">
-      <c r="B11" s="52"/>
-      <c r="C11" s="53"/>
-      <c r="D11" s="53"/>
-      <c r="E11" s="53"/>
-      <c r="F11" s="53"/>
-      <c r="G11" s="53"/>
-      <c r="H11" s="53"/>
-      <c r="I11" s="53"/>
-      <c r="J11" s="54"/>
+      <c r="B11" s="54"/>
+      <c r="C11" s="55"/>
+      <c r="D11" s="55"/>
+      <c r="E11" s="55"/>
+      <c r="F11" s="55"/>
+      <c r="G11" s="55"/>
+      <c r="H11" s="55"/>
+      <c r="I11" s="55"/>
+      <c r="J11" s="56"/>
     </row>
     <row r="12" spans="2:11" ht="14.25" thickBot="1">
-      <c r="B12" s="55"/>
-      <c r="C12" s="56"/>
-      <c r="D12" s="56"/>
-      <c r="E12" s="56"/>
-      <c r="F12" s="56"/>
-      <c r="G12" s="56"/>
-      <c r="H12" s="56"/>
-      <c r="I12" s="56"/>
-      <c r="J12" s="57"/>
+      <c r="B12" s="57"/>
+      <c r="C12" s="58"/>
+      <c r="D12" s="58"/>
+      <c r="E12" s="58"/>
+      <c r="F12" s="58"/>
+      <c r="G12" s="58"/>
+      <c r="H12" s="58"/>
+      <c r="I12" s="58"/>
+      <c r="J12" s="59"/>
     </row>
     <row r="14" spans="2:11" ht="24">
       <c r="B14" s="1" t="s">
@@ -22239,28 +22964,28 @@
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="1:16">
-      <c r="A4" s="63" t="s">
+      <c r="A4" s="65" t="s">
         <v>76</v>
       </c>
-      <c r="B4" s="64"/>
-      <c r="C4" s="64"/>
+      <c r="B4" s="66"/>
+      <c r="C4" s="66"/>
     </row>
     <row r="13" spans="1:16">
-      <c r="A13" s="59" t="s">
+      <c r="A13" s="61" t="s">
         <v>75</v>
       </c>
-      <c r="B13" s="60"/>
-      <c r="C13" s="60"/>
-      <c r="D13" s="59" t="s">
+      <c r="B13" s="62"/>
+      <c r="C13" s="62"/>
+      <c r="D13" s="61" t="s">
         <v>75</v>
       </c>
-      <c r="E13" s="60"/>
-      <c r="F13" s="60"/>
-      <c r="H13" s="65" t="s">
+      <c r="E13" s="62"/>
+      <c r="F13" s="62"/>
+      <c r="H13" s="67" t="s">
         <v>86</v>
       </c>
-      <c r="I13" s="65"/>
-      <c r="J13" s="65"/>
+      <c r="I13" s="67"/>
+      <c r="J13" s="67"/>
     </row>
     <row r="14" spans="1:16" ht="24">
       <c r="A14" s="1" t="s">
@@ -22285,11 +23010,11 @@
       </c>
     </row>
     <row r="24" spans="8:10">
-      <c r="H24" s="62" t="s">
+      <c r="H24" s="64" t="s">
         <v>87</v>
       </c>
-      <c r="I24" s="62"/>
-      <c r="J24" s="62"/>
+      <c r="I24" s="64"/>
+      <c r="J24" s="64"/>
     </row>
     <row r="29" spans="8:10">
       <c r="H29">
@@ -22570,18 +23295,18 @@
       </c>
     </row>
     <row r="4" spans="1:11">
-      <c r="H4" s="63" t="s">
+      <c r="H4" s="65" t="s">
         <v>76</v>
       </c>
-      <c r="I4" s="64"/>
-      <c r="J4" s="64"/>
+      <c r="I4" s="66"/>
+      <c r="J4" s="66"/>
     </row>
     <row r="13" spans="1:11">
-      <c r="H13" s="59" t="s">
+      <c r="H13" s="61" t="s">
         <v>75</v>
       </c>
-      <c r="I13" s="60"/>
-      <c r="J13" s="60"/>
+      <c r="I13" s="62"/>
+      <c r="J13" s="62"/>
     </row>
     <row r="14" spans="1:11" ht="24">
       <c r="H14" s="1" t="s">
@@ -23057,17 +23782,17 @@
       <c r="B3" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="F3" s="66" t="s">
+      <c r="F3" s="68" t="s">
         <v>113</v>
       </c>
-      <c r="G3" s="66"/>
-      <c r="H3" s="66"/>
-      <c r="I3" s="66"/>
-      <c r="J3" s="66"/>
-      <c r="K3" s="66"/>
-      <c r="L3" s="66"/>
-      <c r="M3" s="66"/>
-      <c r="N3" s="66"/>
+      <c r="G3" s="68"/>
+      <c r="H3" s="68"/>
+      <c r="I3" s="68"/>
+      <c r="J3" s="68"/>
+      <c r="K3" s="68"/>
+      <c r="L3" s="68"/>
+      <c r="M3" s="68"/>
+      <c r="N3" s="68"/>
     </row>
     <row r="4" spans="1:14" ht="24">
       <c r="G4" s="7" t="s">
@@ -23093,17 +23818,17 @@
       <c r="B14" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="F14" s="66" t="s">
+      <c r="F14" s="68" t="s">
         <v>115</v>
       </c>
-      <c r="G14" s="66"/>
-      <c r="H14" s="66"/>
-      <c r="I14" s="66"/>
-      <c r="J14" s="66"/>
-      <c r="K14" s="66"/>
-      <c r="L14" s="66"/>
-      <c r="M14" s="66"/>
-      <c r="N14" s="66"/>
+      <c r="G14" s="68"/>
+      <c r="H14" s="68"/>
+      <c r="I14" s="68"/>
+      <c r="J14" s="68"/>
+      <c r="K14" s="68"/>
+      <c r="L14" s="68"/>
+      <c r="M14" s="68"/>
+      <c r="N14" s="68"/>
     </row>
     <row r="15" spans="1:14" ht="24">
       <c r="J15" s="11" t="s">
@@ -23117,17 +23842,17 @@
       <c r="B25" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="F25" s="67" t="s">
+      <c r="F25" s="69" t="s">
         <v>117</v>
       </c>
-      <c r="G25" s="68"/>
-      <c r="H25" s="68"/>
-      <c r="I25" s="68"/>
-      <c r="J25" s="68"/>
-      <c r="K25" s="68"/>
-      <c r="L25" s="68"/>
-      <c r="M25" s="68"/>
-      <c r="N25" s="68"/>
+      <c r="G25" s="70"/>
+      <c r="H25" s="70"/>
+      <c r="I25" s="70"/>
+      <c r="J25" s="70"/>
+      <c r="K25" s="70"/>
+      <c r="L25" s="70"/>
+      <c r="M25" s="70"/>
+      <c r="N25" s="70"/>
     </row>
     <row r="26" spans="1:14" ht="24">
       <c r="J26" s="11" t="s">
@@ -23324,25 +24049,25 @@
       <c r="B3" s="11" t="s">
         <v>136</v>
       </c>
-      <c r="F3" s="66" t="s">
+      <c r="F3" s="68" t="s">
         <v>123</v>
       </c>
-      <c r="G3" s="66"/>
-      <c r="H3" s="66"/>
-      <c r="I3" s="66"/>
-      <c r="J3" s="66"/>
-      <c r="K3" s="66"/>
-      <c r="L3" s="66"/>
-      <c r="M3" s="66"/>
-      <c r="N3" s="66"/>
-      <c r="O3" s="69" t="s">
+      <c r="G3" s="68"/>
+      <c r="H3" s="68"/>
+      <c r="I3" s="68"/>
+      <c r="J3" s="68"/>
+      <c r="K3" s="68"/>
+      <c r="L3" s="68"/>
+      <c r="M3" s="68"/>
+      <c r="N3" s="68"/>
+      <c r="O3" s="71" t="s">
         <v>121</v>
       </c>
-      <c r="P3" s="70"/>
-      <c r="Q3" s="71" t="s">
+      <c r="P3" s="72"/>
+      <c r="Q3" s="73" t="s">
         <v>99</v>
       </c>
-      <c r="R3" s="72"/>
+      <c r="R3" s="74"/>
     </row>
     <row r="4" spans="1:18" ht="24">
       <c r="B4" s="11" t="s">
@@ -23352,10 +24077,10 @@
         <v>76</v>
       </c>
       <c r="H4" s="8"/>
-      <c r="I4" s="73" t="s">
+      <c r="I4" s="75" t="s">
         <v>128</v>
       </c>
-      <c r="J4" s="73"/>
+      <c r="J4" s="75"/>
       <c r="K4" s="11" t="s">
         <v>122</v>
       </c>
@@ -23380,34 +24105,34 @@
       <c r="B14" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="F14" s="66" t="s">
+      <c r="F14" s="68" t="s">
         <v>125</v>
       </c>
-      <c r="G14" s="66"/>
-      <c r="H14" s="66"/>
-      <c r="I14" s="66"/>
-      <c r="J14" s="66"/>
-      <c r="K14" s="66"/>
-      <c r="L14" s="66"/>
-      <c r="M14" s="66"/>
-      <c r="N14" s="66"/>
-      <c r="O14" s="74" t="s">
+      <c r="G14" s="68"/>
+      <c r="H14" s="68"/>
+      <c r="I14" s="68"/>
+      <c r="J14" s="68"/>
+      <c r="K14" s="68"/>
+      <c r="L14" s="68"/>
+      <c r="M14" s="68"/>
+      <c r="N14" s="68"/>
+      <c r="O14" s="76" t="s">
         <v>135</v>
       </c>
-      <c r="P14" s="75"/>
-      <c r="Q14" s="75" t="s">
+      <c r="P14" s="77"/>
+      <c r="Q14" s="77" t="s">
         <v>99</v>
       </c>
-      <c r="R14" s="76"/>
+      <c r="R14" s="78"/>
     </row>
     <row r="15" spans="1:18" ht="24">
       <c r="B15" s="11" t="s">
         <v>132</v>
       </c>
-      <c r="I15" s="73" t="s">
+      <c r="I15" s="75" t="s">
         <v>128</v>
       </c>
-      <c r="J15" s="73"/>
+      <c r="J15" s="75"/>
       <c r="K15" s="11">
         <v>45</v>
       </c>
@@ -23425,17 +24150,17 @@
       <c r="B25" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="F25" s="67" t="s">
+      <c r="F25" s="69" t="s">
         <v>133</v>
       </c>
-      <c r="G25" s="68"/>
-      <c r="H25" s="68"/>
-      <c r="I25" s="68"/>
-      <c r="J25" s="68"/>
-      <c r="K25" s="68"/>
-      <c r="L25" s="68"/>
-      <c r="M25" s="68"/>
-      <c r="N25" s="68"/>
+      <c r="G25" s="70"/>
+      <c r="H25" s="70"/>
+      <c r="I25" s="70"/>
+      <c r="J25" s="70"/>
+      <c r="K25" s="70"/>
+      <c r="L25" s="70"/>
+      <c r="M25" s="70"/>
+      <c r="N25" s="70"/>
     </row>
     <row r="26" spans="1:14" ht="24">
       <c r="B26" s="11" t="s">
@@ -23707,22 +24432,22 @@
       <c r="H3" s="12"/>
       <c r="I3" s="12"/>
       <c r="J3" s="12"/>
-      <c r="K3" s="74" t="s">
+      <c r="K3" s="76" t="s">
         <v>143</v>
       </c>
-      <c r="L3" s="75"/>
-      <c r="M3" s="75" t="s">
+      <c r="L3" s="77"/>
+      <c r="M3" s="77" t="s">
         <v>110</v>
       </c>
-      <c r="N3" s="76"/>
-      <c r="O3" s="69" t="s">
+      <c r="N3" s="78"/>
+      <c r="O3" s="71" t="s">
         <v>144</v>
       </c>
-      <c r="P3" s="70"/>
-      <c r="Q3" s="69" t="s">
+      <c r="P3" s="72"/>
+      <c r="Q3" s="71" t="s">
         <v>110</v>
       </c>
-      <c r="R3" s="70"/>
+      <c r="R3" s="72"/>
     </row>
     <row r="4" spans="1:18" ht="24">
       <c r="A4" t="s">
@@ -23733,8 +24458,8 @@
         <v>76</v>
       </c>
       <c r="H4" s="8"/>
-      <c r="I4" s="73"/>
-      <c r="J4" s="73"/>
+      <c r="I4" s="75"/>
+      <c r="J4" s="75"/>
       <c r="K4" s="11"/>
       <c r="L4" s="11"/>
       <c r="M4" s="11"/>
@@ -23760,27 +24485,27 @@
       <c r="H14" s="12"/>
       <c r="I14" s="12"/>
       <c r="J14" s="12"/>
-      <c r="K14" s="74" t="s">
+      <c r="K14" s="76" t="s">
         <v>135</v>
       </c>
-      <c r="L14" s="75"/>
-      <c r="M14" s="75" t="s">
+      <c r="L14" s="77"/>
+      <c r="M14" s="77" t="s">
         <v>99</v>
       </c>
-      <c r="N14" s="76"/>
-      <c r="O14" s="69" t="s">
+      <c r="N14" s="78"/>
+      <c r="O14" s="71" t="s">
         <v>121</v>
       </c>
-      <c r="P14" s="70"/>
-      <c r="Q14" s="69" t="s">
+      <c r="P14" s="72"/>
+      <c r="Q14" s="71" t="s">
         <v>99</v>
       </c>
-      <c r="R14" s="70"/>
+      <c r="R14" s="72"/>
     </row>
     <row r="15" spans="1:18" ht="24">
       <c r="B15" s="11"/>
-      <c r="I15" s="73"/>
-      <c r="J15" s="73"/>
+      <c r="I15" s="75"/>
+      <c r="J15" s="75"/>
       <c r="K15" s="11"/>
       <c r="L15" s="11"/>
       <c r="M15" s="11"/>
@@ -23792,17 +24517,17 @@
       <c r="B25" s="11" t="s">
         <v>142</v>
       </c>
-      <c r="F25" s="67">
+      <c r="F25" s="69">
         <v>2</v>
       </c>
-      <c r="G25" s="68"/>
-      <c r="H25" s="68"/>
-      <c r="I25" s="68"/>
-      <c r="J25" s="68"/>
-      <c r="K25" s="68"/>
-      <c r="L25" s="68"/>
-      <c r="M25" s="68"/>
-      <c r="N25" s="68"/>
+      <c r="G25" s="70"/>
+      <c r="H25" s="70"/>
+      <c r="I25" s="70"/>
+      <c r="J25" s="70"/>
+      <c r="K25" s="70"/>
+      <c r="L25" s="70"/>
+      <c r="M25" s="70"/>
+      <c r="N25" s="70"/>
     </row>
     <row r="26" spans="1:14" ht="24">
       <c r="B26" s="11"/>
@@ -24137,14 +24862,14 @@
       <c r="K4" s="11"/>
       <c r="L4" s="11"/>
       <c r="M4" s="11"/>
-      <c r="O4" s="69" t="s">
+      <c r="O4" s="71" t="s">
         <v>121</v>
       </c>
-      <c r="P4" s="70"/>
-      <c r="Q4" s="69" t="s">
+      <c r="P4" s="72"/>
+      <c r="Q4" s="71" t="s">
         <v>99</v>
       </c>
-      <c r="R4" s="70"/>
+      <c r="R4" s="72"/>
     </row>
     <row r="13" spans="1:18">
       <c r="G13" s="7" t="s">
@@ -24195,14 +24920,14 @@
       <c r="K18" s="11"/>
       <c r="L18" s="11"/>
       <c r="M18" s="11"/>
-      <c r="O18" s="69" t="s">
+      <c r="O18" s="71" t="s">
         <v>144</v>
       </c>
-      <c r="P18" s="70"/>
-      <c r="Q18" s="69" t="s">
+      <c r="P18" s="72"/>
+      <c r="Q18" s="71" t="s">
         <v>110</v>
       </c>
-      <c r="R18" s="70"/>
+      <c r="R18" s="72"/>
     </row>
     <row r="31" spans="1:18" ht="24">
       <c r="A31" t="s">
@@ -24234,14 +24959,14 @@
       <c r="K32" s="11"/>
       <c r="L32" s="11"/>
       <c r="M32" s="11"/>
-      <c r="O32" s="74" t="s">
+      <c r="O32" s="76" t="s">
         <v>152</v>
       </c>
-      <c r="P32" s="75"/>
-      <c r="Q32" s="77" t="s">
+      <c r="P32" s="77"/>
+      <c r="Q32" s="79" t="s">
         <v>148</v>
       </c>
-      <c r="R32" s="75"/>
+      <c r="R32" s="77"/>
     </row>
     <row r="46" spans="1:18" ht="24">
       <c r="A46" t="s">
@@ -24998,10 +25723,10 @@
       <c r="K32" s="11"/>
       <c r="L32" s="11"/>
       <c r="M32" s="11"/>
-      <c r="O32" s="78"/>
-      <c r="P32" s="79"/>
-      <c r="Q32" s="80"/>
-      <c r="R32" s="79"/>
+      <c r="O32" s="80"/>
+      <c r="P32" s="81"/>
+      <c r="Q32" s="82"/>
+      <c r="R32" s="81"/>
     </row>
     <row r="46" spans="1:18" ht="24">
       <c r="A46" t="s">
@@ -25740,10 +26465,10 @@
       <c r="K32" s="11"/>
       <c r="L32" s="11"/>
       <c r="M32" s="11"/>
-      <c r="O32" s="78"/>
-      <c r="P32" s="79"/>
-      <c r="Q32" s="80"/>
-      <c r="R32" s="79"/>
+      <c r="O32" s="80"/>
+      <c r="P32" s="81"/>
+      <c r="Q32" s="82"/>
+      <c r="R32" s="81"/>
     </row>
     <row r="46" spans="1:18" ht="24">
       <c r="A46" t="s">
@@ -26378,39 +27103,39 @@
     </row>
     <row r="9" spans="2:12" ht="14.25" thickBot="1"/>
     <row r="10" spans="2:12" ht="13.5" customHeight="1">
-      <c r="B10" s="49" t="s">
+      <c r="B10" s="51" t="s">
         <v>81</v>
       </c>
-      <c r="C10" s="50"/>
-      <c r="D10" s="50"/>
-      <c r="E10" s="50"/>
-      <c r="F10" s="50"/>
-      <c r="G10" s="50"/>
-      <c r="H10" s="50"/>
-      <c r="I10" s="50"/>
-      <c r="J10" s="51"/>
+      <c r="C10" s="52"/>
+      <c r="D10" s="52"/>
+      <c r="E10" s="52"/>
+      <c r="F10" s="52"/>
+      <c r="G10" s="52"/>
+      <c r="H10" s="52"/>
+      <c r="I10" s="52"/>
+      <c r="J10" s="53"/>
     </row>
     <row r="11" spans="2:12" ht="13.5" customHeight="1">
-      <c r="B11" s="52"/>
-      <c r="C11" s="53"/>
-      <c r="D11" s="53"/>
-      <c r="E11" s="53"/>
-      <c r="F11" s="53"/>
-      <c r="G11" s="53"/>
-      <c r="H11" s="53"/>
-      <c r="I11" s="53"/>
-      <c r="J11" s="54"/>
+      <c r="B11" s="54"/>
+      <c r="C11" s="55"/>
+      <c r="D11" s="55"/>
+      <c r="E11" s="55"/>
+      <c r="F11" s="55"/>
+      <c r="G11" s="55"/>
+      <c r="H11" s="55"/>
+      <c r="I11" s="55"/>
+      <c r="J11" s="56"/>
     </row>
     <row r="12" spans="2:12" ht="13.5" customHeight="1" thickBot="1">
-      <c r="B12" s="55"/>
-      <c r="C12" s="56"/>
-      <c r="D12" s="56"/>
-      <c r="E12" s="56"/>
-      <c r="F12" s="56"/>
-      <c r="G12" s="56"/>
-      <c r="H12" s="56"/>
-      <c r="I12" s="56"/>
-      <c r="J12" s="57"/>
+      <c r="B12" s="57"/>
+      <c r="C12" s="58"/>
+      <c r="D12" s="58"/>
+      <c r="E12" s="58"/>
+      <c r="F12" s="58"/>
+      <c r="G12" s="58"/>
+      <c r="H12" s="58"/>
+      <c r="I12" s="58"/>
+      <c r="J12" s="59"/>
     </row>
     <row r="14" spans="2:12" ht="24">
       <c r="B14" s="1" t="s">
@@ -26768,10 +27493,10 @@
       <c r="K32" s="11"/>
       <c r="L32" s="11"/>
       <c r="M32" s="11"/>
-      <c r="O32" s="78"/>
-      <c r="P32" s="79"/>
-      <c r="Q32" s="80"/>
-      <c r="R32" s="79"/>
+      <c r="O32" s="80"/>
+      <c r="P32" s="81"/>
+      <c r="Q32" s="82"/>
+      <c r="R32" s="81"/>
     </row>
     <row r="46" spans="1:18" ht="24">
       <c r="A46" t="s">
@@ -28762,13 +29487,13 @@
       <c r="F14" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="G14" s="81" t="s">
+      <c r="G14" s="83" t="s">
         <v>279</v>
       </c>
-      <c r="H14" s="81"/>
-      <c r="I14" s="81"/>
-      <c r="J14" s="81"/>
-      <c r="K14" s="81"/>
+      <c r="H14" s="83"/>
+      <c r="I14" s="83"/>
+      <c r="J14" s="83"/>
+      <c r="K14" s="83"/>
     </row>
     <row r="15" spans="1:18" ht="24">
       <c r="B15" s="11"/>
@@ -28866,9 +29591,9 @@
               </from>
               <to>
                 <xdr:col>4</xdr:col>
-                <xdr:colOff>552450</xdr:colOff>
-                <xdr:row>24</xdr:row>
-                <xdr:rowOff>114300</xdr:rowOff>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>22</xdr:row>
+                <xdr:rowOff>28575</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
@@ -28893,7 +29618,7 @@
                 <xdr:col>4</xdr:col>
                 <xdr:colOff>409575</xdr:colOff>
                 <xdr:row>10</xdr:row>
-                <xdr:rowOff>28575</xdr:rowOff>
+                <xdr:rowOff>19050</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
@@ -28960,11 +29685,11 @@
       <c r="F13" s="11" t="s">
         <v>284</v>
       </c>
-      <c r="G13" s="84"/>
-      <c r="H13" s="84"/>
-      <c r="I13" s="84"/>
-      <c r="J13" s="84"/>
-      <c r="K13" s="84"/>
+      <c r="G13" s="50"/>
+      <c r="H13" s="50"/>
+      <c r="I13" s="50"/>
+      <c r="J13" s="50"/>
+      <c r="K13" s="50"/>
     </row>
     <row r="14" spans="1:18" ht="24">
       <c r="B14" s="11"/>
@@ -29027,11 +29752,11 @@
       <c r="F29" s="11" t="s">
         <v>285</v>
       </c>
-      <c r="G29" s="84"/>
-      <c r="H29" s="84"/>
-      <c r="I29" s="84"/>
-      <c r="J29" s="84"/>
-      <c r="K29" s="84"/>
+      <c r="G29" s="50"/>
+      <c r="H29" s="50"/>
+      <c r="I29" s="50"/>
+      <c r="J29" s="50"/>
+      <c r="K29" s="50"/>
     </row>
     <row r="30" spans="1:18" ht="24">
       <c r="B30" s="11"/>
@@ -29093,10 +29818,10 @@
                 <xdr:rowOff>38100</xdr:rowOff>
               </from>
               <to>
-                <xdr:col>10</xdr:col>
-                <xdr:colOff>285750</xdr:colOff>
-                <xdr:row>39</xdr:row>
-                <xdr:rowOff>9525</xdr:rowOff>
+                <xdr:col>9</xdr:col>
+                <xdr:colOff>571500</xdr:colOff>
+                <xdr:row>37</xdr:row>
+                <xdr:rowOff>28575</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
@@ -29119,9 +29844,9 @@
               </from>
               <to>
                 <xdr:col>4</xdr:col>
-                <xdr:colOff>552450</xdr:colOff>
-                <xdr:row>39</xdr:row>
-                <xdr:rowOff>114300</xdr:rowOff>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>37</xdr:row>
+                <xdr:rowOff>28575</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
@@ -29171,7 +29896,7 @@
                 <xdr:col>9</xdr:col>
                 <xdr:colOff>561975</xdr:colOff>
                 <xdr:row>10</xdr:row>
-                <xdr:rowOff>28575</xdr:rowOff>
+                <xdr:rowOff>19050</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
@@ -29196,7 +29921,7 @@
                 <xdr:col>4</xdr:col>
                 <xdr:colOff>409575</xdr:colOff>
                 <xdr:row>10</xdr:row>
-                <xdr:rowOff>28575</xdr:rowOff>
+                <xdr:rowOff>19050</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
@@ -29219,9 +29944,9 @@
               </from>
               <to>
                 <xdr:col>4</xdr:col>
-                <xdr:colOff>552450</xdr:colOff>
-                <xdr:row>23</xdr:row>
-                <xdr:rowOff>114300</xdr:rowOff>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>21</xdr:row>
+                <xdr:rowOff>28575</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
@@ -29236,6 +29961,545 @@
 </file>
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Sheet29"/>
+  <dimension ref="A1:R71"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <cols>
+    <col min="5" max="5" width="9" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" ht="24">
+      <c r="A1" s="1"/>
+      <c r="D1" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="K1" s="14"/>
+      <c r="L1" s="15"/>
+      <c r="M1" s="15"/>
+      <c r="N1" s="16"/>
+      <c r="O1" s="17"/>
+      <c r="P1" s="18"/>
+      <c r="Q1" s="17"/>
+      <c r="R1" s="18"/>
+    </row>
+    <row r="2" spans="1:18" ht="24">
+      <c r="A2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="K2" s="38"/>
+      <c r="L2" s="39"/>
+      <c r="M2" s="39"/>
+      <c r="N2" s="39"/>
+      <c r="O2" s="40"/>
+      <c r="P2" s="41"/>
+      <c r="Q2" s="40"/>
+      <c r="R2" s="41"/>
+    </row>
+    <row r="3" spans="1:18">
+      <c r="D3" s="49" t="s">
+        <v>224</v>
+      </c>
+      <c r="I3" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" ht="24">
+      <c r="A13" t="s">
+        <v>100</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>283</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>286</v>
+      </c>
+      <c r="G13" s="50"/>
+      <c r="H13" s="50"/>
+      <c r="I13" s="50"/>
+      <c r="J13" s="50"/>
+      <c r="K13" s="50"/>
+    </row>
+    <row r="14" spans="1:18" ht="24">
+      <c r="B14" s="11"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="7"/>
+      <c r="H14" s="7"/>
+      <c r="I14" s="7"/>
+      <c r="J14" s="11"/>
+      <c r="K14" s="11"/>
+      <c r="L14" s="11"/>
+      <c r="M14" s="11"/>
+      <c r="O14" s="17"/>
+      <c r="P14" s="18"/>
+      <c r="Q14" s="17"/>
+      <c r="R14" s="18"/>
+    </row>
+    <row r="23" spans="1:18">
+      <c r="G23" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="H23" s="8"/>
+      <c r="I23" s="8"/>
+    </row>
+    <row r="24" spans="1:18">
+      <c r="G24" s="7"/>
+      <c r="H24" s="8"/>
+      <c r="I24" s="8"/>
+    </row>
+    <row r="25" spans="1:18">
+      <c r="B25" t="s">
+        <v>274</v>
+      </c>
+      <c r="G25" s="7"/>
+      <c r="H25" s="8"/>
+      <c r="I25" s="8"/>
+    </row>
+    <row r="26" spans="1:18">
+      <c r="G26" s="7"/>
+      <c r="H26" s="8"/>
+      <c r="I26" s="8"/>
+    </row>
+    <row r="27" spans="1:18">
+      <c r="G27" s="7"/>
+      <c r="H27" s="8"/>
+      <c r="I27" s="8"/>
+    </row>
+    <row r="28" spans="1:18">
+      <c r="B28" s="47"/>
+      <c r="G28" s="7"/>
+      <c r="H28" s="8"/>
+      <c r="I28" s="8"/>
+    </row>
+    <row r="29" spans="1:18" ht="24">
+      <c r="A29" t="s">
+        <v>100</v>
+      </c>
+      <c r="B29" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="F29" s="11" t="s">
+        <v>287</v>
+      </c>
+      <c r="G29" s="50"/>
+      <c r="H29" s="50"/>
+      <c r="I29" s="50"/>
+      <c r="J29" s="50"/>
+      <c r="K29" s="50"/>
+    </row>
+    <row r="30" spans="1:18" ht="24">
+      <c r="B30" s="11"/>
+      <c r="F30" s="1"/>
+      <c r="G30" s="7"/>
+      <c r="H30" s="7"/>
+      <c r="I30" s="7"/>
+      <c r="J30" s="11"/>
+      <c r="K30" s="11"/>
+      <c r="L30" s="11"/>
+      <c r="M30" s="11"/>
+      <c r="O30" s="17"/>
+      <c r="P30" s="18"/>
+      <c r="Q30" s="17"/>
+      <c r="R30" s="18"/>
+    </row>
+    <row r="39" spans="1:18">
+      <c r="G39" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="H39" s="8"/>
+      <c r="I39" s="8"/>
+    </row>
+    <row r="40" spans="1:18">
+      <c r="G40" s="7"/>
+      <c r="H40" s="8"/>
+      <c r="I40" s="8"/>
+    </row>
+    <row r="41" spans="1:18">
+      <c r="B41" t="s">
+        <v>274</v>
+      </c>
+      <c r="G41" s="7"/>
+      <c r="H41" s="8"/>
+      <c r="I41" s="8"/>
+    </row>
+    <row r="42" spans="1:18">
+      <c r="B42" s="47"/>
+      <c r="G42" s="7"/>
+      <c r="H42" s="8"/>
+      <c r="I42" s="8"/>
+    </row>
+    <row r="43" spans="1:18" ht="24">
+      <c r="A43" t="s">
+        <v>110</v>
+      </c>
+      <c r="B43" s="11" t="s">
+        <v>160</v>
+      </c>
+      <c r="F43" s="11" t="s">
+        <v>288</v>
+      </c>
+      <c r="G43" s="50"/>
+      <c r="H43" s="50"/>
+      <c r="I43" s="50"/>
+      <c r="J43" s="50"/>
+      <c r="K43" s="50"/>
+    </row>
+    <row r="44" spans="1:18" ht="24">
+      <c r="B44" s="11"/>
+      <c r="F44" s="1"/>
+      <c r="G44" s="7"/>
+      <c r="H44" s="7"/>
+      <c r="I44" s="7"/>
+      <c r="J44" s="11"/>
+      <c r="K44" s="11"/>
+      <c r="L44" s="11"/>
+      <c r="M44" s="11"/>
+      <c r="O44" s="17"/>
+      <c r="P44" s="18"/>
+      <c r="Q44" s="17"/>
+      <c r="R44" s="18"/>
+    </row>
+    <row r="53" spans="1:18">
+      <c r="G53" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="H53" s="8"/>
+      <c r="I53" s="8"/>
+    </row>
+    <row r="54" spans="1:18">
+      <c r="G54" s="7"/>
+      <c r="H54" s="8"/>
+      <c r="I54" s="8"/>
+    </row>
+    <row r="55" spans="1:18">
+      <c r="B55" t="s">
+        <v>274</v>
+      </c>
+      <c r="G55" s="7"/>
+      <c r="H55" s="8"/>
+      <c r="I55" s="8"/>
+    </row>
+    <row r="56" spans="1:18">
+      <c r="B56" s="47"/>
+      <c r="G56" s="7"/>
+      <c r="H56" s="8"/>
+      <c r="I56" s="8"/>
+    </row>
+    <row r="57" spans="1:18" ht="24">
+      <c r="A57" t="s">
+        <v>110</v>
+      </c>
+      <c r="B57" s="11" t="s">
+        <v>290</v>
+      </c>
+      <c r="F57" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="G57" s="50"/>
+      <c r="H57" s="50"/>
+      <c r="I57" s="50"/>
+      <c r="J57" s="50"/>
+      <c r="K57" s="50"/>
+    </row>
+    <row r="58" spans="1:18" ht="24">
+      <c r="B58" s="11"/>
+      <c r="F58" s="1"/>
+      <c r="G58" s="7"/>
+      <c r="H58" s="7"/>
+      <c r="I58" s="7"/>
+      <c r="J58" s="11"/>
+      <c r="K58" s="11"/>
+      <c r="L58" s="11"/>
+      <c r="M58" s="11"/>
+      <c r="O58" s="17"/>
+      <c r="P58" s="18"/>
+      <c r="Q58" s="17"/>
+      <c r="R58" s="18"/>
+    </row>
+    <row r="67" spans="2:9">
+      <c r="G67" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="H67" s="8"/>
+      <c r="I67" s="8"/>
+    </row>
+    <row r="68" spans="2:9">
+      <c r="G68" s="7"/>
+      <c r="H68" s="8"/>
+      <c r="I68" s="8"/>
+    </row>
+    <row r="69" spans="2:9">
+      <c r="B69" t="s">
+        <v>274</v>
+      </c>
+      <c r="G69" s="7"/>
+      <c r="H69" s="8"/>
+      <c r="I69" s="8"/>
+    </row>
+    <row r="71" spans="2:9">
+      <c r="F71" s="86"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.35433070866141736" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
+  <controls>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="55306" r:id="rId4" name="BarCodeCtrl10">
+          <controlPr defaultSize="0" autoLine="0" linkedCell="F57" r:id="rId5">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>8</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>57</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>10</xdr:col>
+                <xdr:colOff>219075</xdr:colOff>
+                <xdr:row>65</xdr:row>
+                <xdr:rowOff>9525</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="55306" r:id="rId4" name="BarCodeCtrl10"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="55305" r:id="rId6" name="BarCodeCtrl9">
+          <controlPr defaultSize="0" autoLine="0" linkedCell="B57" r:id="rId7">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>123825</xdr:colOff>
+                <xdr:row>57</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>4</xdr:col>
+                <xdr:colOff>495300</xdr:colOff>
+                <xdr:row>65</xdr:row>
+                <xdr:rowOff>114300</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="55305" r:id="rId6" name="BarCodeCtrl9"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="55304" r:id="rId8" name="BarCodeCtrl8">
+          <controlPr defaultSize="0" autoLine="0" autoPict="0" linkedCell="F43" r:id="rId9">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>8</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>42</xdr:row>
+                <xdr:rowOff>295275</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>10</xdr:col>
+                <xdr:colOff>219075</xdr:colOff>
+                <xdr:row>50</xdr:row>
+                <xdr:rowOff>152400</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="55304" r:id="rId8" name="BarCodeCtrl8"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="55303" r:id="rId10" name="BarCodeCtrl7">
+          <controlPr defaultSize="0" autoLine="0" linkedCell="B43" r:id="rId11">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>123825</xdr:colOff>
+                <xdr:row>43</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>4</xdr:col>
+                <xdr:colOff>495300</xdr:colOff>
+                <xdr:row>51</xdr:row>
+                <xdr:rowOff>114300</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="55303" r:id="rId10" name="BarCodeCtrl7"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="55297" r:id="rId12" name="BarCodeCtrl2">
+          <controlPr defaultSize="0" autoLine="0" linkedCell="B13" r:id="rId13">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>666750</xdr:colOff>
+                <xdr:row>13</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>6</xdr:col>
+                <xdr:colOff>342900</xdr:colOff>
+                <xdr:row>21</xdr:row>
+                <xdr:rowOff>133350</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="55297" r:id="rId12" name="BarCodeCtrl2"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="55298" r:id="rId14" name="BarCodeCtrl5">
+          <controlPr defaultSize="0" autoLine="0" r:id="rId15">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>590550</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>28575</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>4</xdr:col>
+                <xdr:colOff>409575</xdr:colOff>
+                <xdr:row>10</xdr:row>
+                <xdr:rowOff>28575</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="55298" r:id="rId14" name="BarCodeCtrl5"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="55299" r:id="rId16" name="BarCodeCtrl3">
+          <controlPr defaultSize="0" autoLine="0" r:id="rId17">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>8</xdr:col>
+                <xdr:colOff>57150</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>28575</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>9</xdr:col>
+                <xdr:colOff>561975</xdr:colOff>
+                <xdr:row>10</xdr:row>
+                <xdr:rowOff>28575</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="55299" r:id="rId16" name="BarCodeCtrl3"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="55300" r:id="rId18" name="BarCodeCtrl1">
+          <controlPr defaultSize="0" autoLine="0" linkedCell="F13" r:id="rId19">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>12</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>13</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>14</xdr:col>
+                <xdr:colOff>219075</xdr:colOff>
+                <xdr:row>21</xdr:row>
+                <xdr:rowOff>28575</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="55300" r:id="rId18" name="BarCodeCtrl1"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="55301" r:id="rId20" name="BarCodeCtrl4">
+          <controlPr defaultSize="0" autoLine="0" linkedCell="B29" r:id="rId21">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>123825</xdr:colOff>
+                <xdr:row>29</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>4</xdr:col>
+                <xdr:colOff>495300</xdr:colOff>
+                <xdr:row>37</xdr:row>
+                <xdr:rowOff>104775</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="55301" r:id="rId20" name="BarCodeCtrl4"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="55302" r:id="rId22" name="BarCodeCtrl6">
+          <controlPr defaultSize="0" autoLine="0" linkedCell="F29" r:id="rId23">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>8</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>28</xdr:row>
+                <xdr:rowOff>295275</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>10</xdr:col>
+                <xdr:colOff>219075</xdr:colOff>
+                <xdr:row>36</xdr:row>
+                <xdr:rowOff>142875</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="55302" r:id="rId22" name="BarCodeCtrl6"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+  </controls>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet20"/>
   <dimension ref="B1:C25"/>
@@ -29458,7 +30722,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet16"/>
   <dimension ref="B1:AB42"/>
@@ -29468,352 +30732,352 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:28">
-      <c r="B1" s="82"/>
-      <c r="C1" s="82"/>
-      <c r="D1" s="82"/>
-      <c r="E1" s="82"/>
-      <c r="F1" s="82"/>
-      <c r="G1" s="82"/>
-      <c r="H1" s="82"/>
-      <c r="I1" s="82"/>
-      <c r="J1" s="82"/>
-      <c r="K1" s="83"/>
-      <c r="L1" s="83"/>
-      <c r="M1" s="83"/>
-      <c r="N1" s="83"/>
-      <c r="O1" s="83"/>
-      <c r="P1" s="83"/>
-      <c r="Q1" s="83"/>
-      <c r="R1" s="83"/>
-      <c r="S1" s="83"/>
-      <c r="T1" s="83"/>
-      <c r="U1" s="83"/>
-      <c r="V1" s="83"/>
-      <c r="W1" s="83"/>
-      <c r="X1" s="83"/>
-      <c r="Y1" s="83"/>
-      <c r="Z1" s="83"/>
-      <c r="AA1" s="83"/>
-      <c r="AB1" s="83"/>
+      <c r="B1" s="84"/>
+      <c r="C1" s="84"/>
+      <c r="D1" s="84"/>
+      <c r="E1" s="84"/>
+      <c r="F1" s="84"/>
+      <c r="G1" s="84"/>
+      <c r="H1" s="84"/>
+      <c r="I1" s="84"/>
+      <c r="J1" s="84"/>
+      <c r="K1" s="85"/>
+      <c r="L1" s="85"/>
+      <c r="M1" s="85"/>
+      <c r="N1" s="85"/>
+      <c r="O1" s="85"/>
+      <c r="P1" s="85"/>
+      <c r="Q1" s="85"/>
+      <c r="R1" s="85"/>
+      <c r="S1" s="85"/>
+      <c r="T1" s="85"/>
+      <c r="U1" s="85"/>
+      <c r="V1" s="85"/>
+      <c r="W1" s="85"/>
+      <c r="X1" s="85"/>
+      <c r="Y1" s="85"/>
+      <c r="Z1" s="85"/>
+      <c r="AA1" s="85"/>
+      <c r="AB1" s="85"/>
     </row>
     <row r="2" spans="2:28">
-      <c r="B2" s="82"/>
-      <c r="C2" s="82"/>
-      <c r="D2" s="82"/>
-      <c r="E2" s="82"/>
-      <c r="F2" s="82"/>
-      <c r="G2" s="82"/>
-      <c r="H2" s="82"/>
-      <c r="I2" s="82"/>
-      <c r="J2" s="82"/>
-      <c r="K2" s="83"/>
-      <c r="L2" s="83"/>
-      <c r="M2" s="83"/>
-      <c r="N2" s="83"/>
-      <c r="O2" s="83"/>
-      <c r="P2" s="83"/>
-      <c r="Q2" s="83"/>
-      <c r="R2" s="83"/>
-      <c r="S2" s="83"/>
-      <c r="T2" s="83"/>
-      <c r="U2" s="83"/>
-      <c r="V2" s="83"/>
-      <c r="W2" s="83"/>
-      <c r="X2" s="83"/>
-      <c r="Y2" s="83"/>
-      <c r="Z2" s="83"/>
-      <c r="AA2" s="83"/>
-      <c r="AB2" s="83"/>
+      <c r="B2" s="84"/>
+      <c r="C2" s="84"/>
+      <c r="D2" s="84"/>
+      <c r="E2" s="84"/>
+      <c r="F2" s="84"/>
+      <c r="G2" s="84"/>
+      <c r="H2" s="84"/>
+      <c r="I2" s="84"/>
+      <c r="J2" s="84"/>
+      <c r="K2" s="85"/>
+      <c r="L2" s="85"/>
+      <c r="M2" s="85"/>
+      <c r="N2" s="85"/>
+      <c r="O2" s="85"/>
+      <c r="P2" s="85"/>
+      <c r="Q2" s="85"/>
+      <c r="R2" s="85"/>
+      <c r="S2" s="85"/>
+      <c r="T2" s="85"/>
+      <c r="U2" s="85"/>
+      <c r="V2" s="85"/>
+      <c r="W2" s="85"/>
+      <c r="X2" s="85"/>
+      <c r="Y2" s="85"/>
+      <c r="Z2" s="85"/>
+      <c r="AA2" s="85"/>
+      <c r="AB2" s="85"/>
     </row>
     <row r="3" spans="2:28">
-      <c r="B3" s="82"/>
-      <c r="C3" s="82"/>
-      <c r="D3" s="82"/>
-      <c r="E3" s="82"/>
-      <c r="F3" s="82"/>
-      <c r="G3" s="82"/>
-      <c r="H3" s="82"/>
-      <c r="I3" s="82"/>
-      <c r="J3" s="82"/>
-      <c r="K3" s="83"/>
-      <c r="L3" s="83"/>
-      <c r="M3" s="83"/>
-      <c r="N3" s="83"/>
-      <c r="O3" s="83"/>
-      <c r="P3" s="83"/>
-      <c r="Q3" s="83"/>
-      <c r="R3" s="83"/>
-      <c r="S3" s="83"/>
-      <c r="T3" s="83"/>
-      <c r="U3" s="83"/>
-      <c r="V3" s="83"/>
-      <c r="W3" s="83"/>
-      <c r="X3" s="83"/>
-      <c r="Y3" s="83"/>
-      <c r="Z3" s="83"/>
-      <c r="AA3" s="83"/>
-      <c r="AB3" s="83"/>
+      <c r="B3" s="84"/>
+      <c r="C3" s="84"/>
+      <c r="D3" s="84"/>
+      <c r="E3" s="84"/>
+      <c r="F3" s="84"/>
+      <c r="G3" s="84"/>
+      <c r="H3" s="84"/>
+      <c r="I3" s="84"/>
+      <c r="J3" s="84"/>
+      <c r="K3" s="85"/>
+      <c r="L3" s="85"/>
+      <c r="M3" s="85"/>
+      <c r="N3" s="85"/>
+      <c r="O3" s="85"/>
+      <c r="P3" s="85"/>
+      <c r="Q3" s="85"/>
+      <c r="R3" s="85"/>
+      <c r="S3" s="85"/>
+      <c r="T3" s="85"/>
+      <c r="U3" s="85"/>
+      <c r="V3" s="85"/>
+      <c r="W3" s="85"/>
+      <c r="X3" s="85"/>
+      <c r="Y3" s="85"/>
+      <c r="Z3" s="85"/>
+      <c r="AA3" s="85"/>
+      <c r="AB3" s="85"/>
     </row>
     <row r="4" spans="2:28">
-      <c r="B4" s="82"/>
-      <c r="C4" s="82"/>
-      <c r="D4" s="82"/>
-      <c r="E4" s="82"/>
-      <c r="F4" s="82"/>
-      <c r="G4" s="82"/>
-      <c r="H4" s="82"/>
-      <c r="I4" s="82"/>
-      <c r="J4" s="82"/>
-      <c r="K4" s="83"/>
-      <c r="L4" s="83"/>
-      <c r="M4" s="83"/>
-      <c r="N4" s="83"/>
-      <c r="O4" s="83"/>
-      <c r="P4" s="83"/>
-      <c r="Q4" s="83"/>
-      <c r="R4" s="83"/>
-      <c r="S4" s="83"/>
-      <c r="T4" s="83"/>
-      <c r="U4" s="83"/>
-      <c r="V4" s="83"/>
-      <c r="W4" s="83"/>
-      <c r="X4" s="83"/>
-      <c r="Y4" s="83"/>
-      <c r="Z4" s="83"/>
-      <c r="AA4" s="83"/>
-      <c r="AB4" s="83"/>
+      <c r="B4" s="84"/>
+      <c r="C4" s="84"/>
+      <c r="D4" s="84"/>
+      <c r="E4" s="84"/>
+      <c r="F4" s="84"/>
+      <c r="G4" s="84"/>
+      <c r="H4" s="84"/>
+      <c r="I4" s="84"/>
+      <c r="J4" s="84"/>
+      <c r="K4" s="85"/>
+      <c r="L4" s="85"/>
+      <c r="M4" s="85"/>
+      <c r="N4" s="85"/>
+      <c r="O4" s="85"/>
+      <c r="P4" s="85"/>
+      <c r="Q4" s="85"/>
+      <c r="R4" s="85"/>
+      <c r="S4" s="85"/>
+      <c r="T4" s="85"/>
+      <c r="U4" s="85"/>
+      <c r="V4" s="85"/>
+      <c r="W4" s="85"/>
+      <c r="X4" s="85"/>
+      <c r="Y4" s="85"/>
+      <c r="Z4" s="85"/>
+      <c r="AA4" s="85"/>
+      <c r="AB4" s="85"/>
     </row>
     <row r="5" spans="2:28">
-      <c r="B5" s="82"/>
-      <c r="C5" s="82"/>
-      <c r="D5" s="82"/>
-      <c r="E5" s="82"/>
-      <c r="F5" s="82"/>
-      <c r="G5" s="82"/>
-      <c r="H5" s="82"/>
-      <c r="I5" s="82"/>
-      <c r="J5" s="82"/>
-      <c r="K5" s="83"/>
-      <c r="L5" s="83"/>
-      <c r="M5" s="83"/>
-      <c r="N5" s="83"/>
-      <c r="O5" s="83"/>
-      <c r="P5" s="83"/>
-      <c r="Q5" s="83"/>
-      <c r="R5" s="83"/>
-      <c r="S5" s="83"/>
-      <c r="T5" s="83"/>
-      <c r="U5" s="83"/>
-      <c r="V5" s="83"/>
-      <c r="W5" s="83"/>
-      <c r="X5" s="83"/>
-      <c r="Y5" s="83"/>
-      <c r="Z5" s="83"/>
-      <c r="AA5" s="83"/>
-      <c r="AB5" s="83"/>
+      <c r="B5" s="84"/>
+      <c r="C5" s="84"/>
+      <c r="D5" s="84"/>
+      <c r="E5" s="84"/>
+      <c r="F5" s="84"/>
+      <c r="G5" s="84"/>
+      <c r="H5" s="84"/>
+      <c r="I5" s="84"/>
+      <c r="J5" s="84"/>
+      <c r="K5" s="85"/>
+      <c r="L5" s="85"/>
+      <c r="M5" s="85"/>
+      <c r="N5" s="85"/>
+      <c r="O5" s="85"/>
+      <c r="P5" s="85"/>
+      <c r="Q5" s="85"/>
+      <c r="R5" s="85"/>
+      <c r="S5" s="85"/>
+      <c r="T5" s="85"/>
+      <c r="U5" s="85"/>
+      <c r="V5" s="85"/>
+      <c r="W5" s="85"/>
+      <c r="X5" s="85"/>
+      <c r="Y5" s="85"/>
+      <c r="Z5" s="85"/>
+      <c r="AA5" s="85"/>
+      <c r="AB5" s="85"/>
     </row>
     <row r="6" spans="2:28">
-      <c r="B6" s="82"/>
-      <c r="C6" s="82"/>
-      <c r="D6" s="82"/>
-      <c r="E6" s="82"/>
-      <c r="F6" s="82"/>
-      <c r="G6" s="82"/>
-      <c r="H6" s="82"/>
-      <c r="I6" s="82"/>
-      <c r="J6" s="82"/>
-      <c r="K6" s="83"/>
-      <c r="L6" s="83"/>
-      <c r="M6" s="83"/>
-      <c r="N6" s="83"/>
-      <c r="O6" s="83"/>
-      <c r="P6" s="83"/>
-      <c r="Q6" s="83"/>
-      <c r="R6" s="83"/>
-      <c r="S6" s="83"/>
-      <c r="T6" s="83"/>
-      <c r="U6" s="83"/>
-      <c r="V6" s="83"/>
-      <c r="W6" s="83"/>
-      <c r="X6" s="83"/>
-      <c r="Y6" s="83"/>
-      <c r="Z6" s="83"/>
-      <c r="AA6" s="83"/>
-      <c r="AB6" s="83"/>
+      <c r="B6" s="84"/>
+      <c r="C6" s="84"/>
+      <c r="D6" s="84"/>
+      <c r="E6" s="84"/>
+      <c r="F6" s="84"/>
+      <c r="G6" s="84"/>
+      <c r="H6" s="84"/>
+      <c r="I6" s="84"/>
+      <c r="J6" s="84"/>
+      <c r="K6" s="85"/>
+      <c r="L6" s="85"/>
+      <c r="M6" s="85"/>
+      <c r="N6" s="85"/>
+      <c r="O6" s="85"/>
+      <c r="P6" s="85"/>
+      <c r="Q6" s="85"/>
+      <c r="R6" s="85"/>
+      <c r="S6" s="85"/>
+      <c r="T6" s="85"/>
+      <c r="U6" s="85"/>
+      <c r="V6" s="85"/>
+      <c r="W6" s="85"/>
+      <c r="X6" s="85"/>
+      <c r="Y6" s="85"/>
+      <c r="Z6" s="85"/>
+      <c r="AA6" s="85"/>
+      <c r="AB6" s="85"/>
     </row>
     <row r="37" spans="2:28">
-      <c r="B37" s="83"/>
-      <c r="C37" s="83"/>
-      <c r="D37" s="83"/>
-      <c r="E37" s="83"/>
-      <c r="F37" s="83"/>
-      <c r="G37" s="83"/>
-      <c r="H37" s="83"/>
-      <c r="I37" s="83"/>
-      <c r="J37" s="83"/>
-      <c r="K37" s="83"/>
-      <c r="L37" s="83"/>
-      <c r="M37" s="83"/>
-      <c r="N37" s="83"/>
-      <c r="O37" s="83"/>
-      <c r="P37" s="83"/>
-      <c r="Q37" s="83"/>
-      <c r="R37" s="83"/>
-      <c r="S37" s="83"/>
-      <c r="T37" s="83"/>
-      <c r="U37" s="83"/>
-      <c r="V37" s="83"/>
-      <c r="W37" s="83"/>
-      <c r="X37" s="83"/>
-      <c r="Y37" s="83"/>
-      <c r="Z37" s="83"/>
-      <c r="AA37" s="83"/>
-      <c r="AB37" s="83"/>
+      <c r="B37" s="85"/>
+      <c r="C37" s="85"/>
+      <c r="D37" s="85"/>
+      <c r="E37" s="85"/>
+      <c r="F37" s="85"/>
+      <c r="G37" s="85"/>
+      <c r="H37" s="85"/>
+      <c r="I37" s="85"/>
+      <c r="J37" s="85"/>
+      <c r="K37" s="85"/>
+      <c r="L37" s="85"/>
+      <c r="M37" s="85"/>
+      <c r="N37" s="85"/>
+      <c r="O37" s="85"/>
+      <c r="P37" s="85"/>
+      <c r="Q37" s="85"/>
+      <c r="R37" s="85"/>
+      <c r="S37" s="85"/>
+      <c r="T37" s="85"/>
+      <c r="U37" s="85"/>
+      <c r="V37" s="85"/>
+      <c r="W37" s="85"/>
+      <c r="X37" s="85"/>
+      <c r="Y37" s="85"/>
+      <c r="Z37" s="85"/>
+      <c r="AA37" s="85"/>
+      <c r="AB37" s="85"/>
     </row>
     <row r="38" spans="2:28">
-      <c r="B38" s="83"/>
-      <c r="C38" s="83"/>
-      <c r="D38" s="83"/>
-      <c r="E38" s="83"/>
-      <c r="F38" s="83"/>
-      <c r="G38" s="83"/>
-      <c r="H38" s="83"/>
-      <c r="I38" s="83"/>
-      <c r="J38" s="83"/>
-      <c r="K38" s="83"/>
-      <c r="L38" s="83"/>
-      <c r="M38" s="83"/>
-      <c r="N38" s="83"/>
-      <c r="O38" s="83"/>
-      <c r="P38" s="83"/>
-      <c r="Q38" s="83"/>
-      <c r="R38" s="83"/>
-      <c r="S38" s="83"/>
-      <c r="T38" s="83"/>
-      <c r="U38" s="83"/>
-      <c r="V38" s="83"/>
-      <c r="W38" s="83"/>
-      <c r="X38" s="83"/>
-      <c r="Y38" s="83"/>
-      <c r="Z38" s="83"/>
-      <c r="AA38" s="83"/>
-      <c r="AB38" s="83"/>
+      <c r="B38" s="85"/>
+      <c r="C38" s="85"/>
+      <c r="D38" s="85"/>
+      <c r="E38" s="85"/>
+      <c r="F38" s="85"/>
+      <c r="G38" s="85"/>
+      <c r="H38" s="85"/>
+      <c r="I38" s="85"/>
+      <c r="J38" s="85"/>
+      <c r="K38" s="85"/>
+      <c r="L38" s="85"/>
+      <c r="M38" s="85"/>
+      <c r="N38" s="85"/>
+      <c r="O38" s="85"/>
+      <c r="P38" s="85"/>
+      <c r="Q38" s="85"/>
+      <c r="R38" s="85"/>
+      <c r="S38" s="85"/>
+      <c r="T38" s="85"/>
+      <c r="U38" s="85"/>
+      <c r="V38" s="85"/>
+      <c r="W38" s="85"/>
+      <c r="X38" s="85"/>
+      <c r="Y38" s="85"/>
+      <c r="Z38" s="85"/>
+      <c r="AA38" s="85"/>
+      <c r="AB38" s="85"/>
     </row>
     <row r="39" spans="2:28">
-      <c r="B39" s="83"/>
-      <c r="C39" s="83"/>
-      <c r="D39" s="83"/>
-      <c r="E39" s="83"/>
-      <c r="F39" s="83"/>
-      <c r="G39" s="83"/>
-      <c r="H39" s="83"/>
-      <c r="I39" s="83"/>
-      <c r="J39" s="83"/>
-      <c r="K39" s="83"/>
-      <c r="L39" s="83"/>
-      <c r="M39" s="83"/>
-      <c r="N39" s="83"/>
-      <c r="O39" s="83"/>
-      <c r="P39" s="83"/>
-      <c r="Q39" s="83"/>
-      <c r="R39" s="83"/>
-      <c r="S39" s="83"/>
-      <c r="T39" s="83"/>
-      <c r="U39" s="83"/>
-      <c r="V39" s="83"/>
-      <c r="W39" s="83"/>
-      <c r="X39" s="83"/>
-      <c r="Y39" s="83"/>
-      <c r="Z39" s="83"/>
-      <c r="AA39" s="83"/>
-      <c r="AB39" s="83"/>
+      <c r="B39" s="85"/>
+      <c r="C39" s="85"/>
+      <c r="D39" s="85"/>
+      <c r="E39" s="85"/>
+      <c r="F39" s="85"/>
+      <c r="G39" s="85"/>
+      <c r="H39" s="85"/>
+      <c r="I39" s="85"/>
+      <c r="J39" s="85"/>
+      <c r="K39" s="85"/>
+      <c r="L39" s="85"/>
+      <c r="M39" s="85"/>
+      <c r="N39" s="85"/>
+      <c r="O39" s="85"/>
+      <c r="P39" s="85"/>
+      <c r="Q39" s="85"/>
+      <c r="R39" s="85"/>
+      <c r="S39" s="85"/>
+      <c r="T39" s="85"/>
+      <c r="U39" s="85"/>
+      <c r="V39" s="85"/>
+      <c r="W39" s="85"/>
+      <c r="X39" s="85"/>
+      <c r="Y39" s="85"/>
+      <c r="Z39" s="85"/>
+      <c r="AA39" s="85"/>
+      <c r="AB39" s="85"/>
     </row>
     <row r="40" spans="2:28">
-      <c r="B40" s="83"/>
-      <c r="C40" s="83"/>
-      <c r="D40" s="83"/>
-      <c r="E40" s="83"/>
-      <c r="F40" s="83"/>
-      <c r="G40" s="83"/>
-      <c r="H40" s="83"/>
-      <c r="I40" s="83"/>
-      <c r="J40" s="83"/>
-      <c r="K40" s="83"/>
-      <c r="L40" s="83"/>
-      <c r="M40" s="83"/>
-      <c r="N40" s="83"/>
-      <c r="O40" s="83"/>
-      <c r="P40" s="83"/>
-      <c r="Q40" s="83"/>
-      <c r="R40" s="83"/>
-      <c r="S40" s="83"/>
-      <c r="T40" s="83"/>
-      <c r="U40" s="83"/>
-      <c r="V40" s="83"/>
-      <c r="W40" s="83"/>
-      <c r="X40" s="83"/>
-      <c r="Y40" s="83"/>
-      <c r="Z40" s="83"/>
-      <c r="AA40" s="83"/>
-      <c r="AB40" s="83"/>
+      <c r="B40" s="85"/>
+      <c r="C40" s="85"/>
+      <c r="D40" s="85"/>
+      <c r="E40" s="85"/>
+      <c r="F40" s="85"/>
+      <c r="G40" s="85"/>
+      <c r="H40" s="85"/>
+      <c r="I40" s="85"/>
+      <c r="J40" s="85"/>
+      <c r="K40" s="85"/>
+      <c r="L40" s="85"/>
+      <c r="M40" s="85"/>
+      <c r="N40" s="85"/>
+      <c r="O40" s="85"/>
+      <c r="P40" s="85"/>
+      <c r="Q40" s="85"/>
+      <c r="R40" s="85"/>
+      <c r="S40" s="85"/>
+      <c r="T40" s="85"/>
+      <c r="U40" s="85"/>
+      <c r="V40" s="85"/>
+      <c r="W40" s="85"/>
+      <c r="X40" s="85"/>
+      <c r="Y40" s="85"/>
+      <c r="Z40" s="85"/>
+      <c r="AA40" s="85"/>
+      <c r="AB40" s="85"/>
     </row>
     <row r="41" spans="2:28">
-      <c r="B41" s="83"/>
-      <c r="C41" s="83"/>
-      <c r="D41" s="83"/>
-      <c r="E41" s="83"/>
-      <c r="F41" s="83"/>
-      <c r="G41" s="83"/>
-      <c r="H41" s="83"/>
-      <c r="I41" s="83"/>
-      <c r="J41" s="83"/>
-      <c r="K41" s="83"/>
-      <c r="L41" s="83"/>
-      <c r="M41" s="83"/>
-      <c r="N41" s="83"/>
-      <c r="O41" s="83"/>
-      <c r="P41" s="83"/>
-      <c r="Q41" s="83"/>
-      <c r="R41" s="83"/>
-      <c r="S41" s="83"/>
-      <c r="T41" s="83"/>
-      <c r="U41" s="83"/>
-      <c r="V41" s="83"/>
-      <c r="W41" s="83"/>
-      <c r="X41" s="83"/>
-      <c r="Y41" s="83"/>
-      <c r="Z41" s="83"/>
-      <c r="AA41" s="83"/>
-      <c r="AB41" s="83"/>
+      <c r="B41" s="85"/>
+      <c r="C41" s="85"/>
+      <c r="D41" s="85"/>
+      <c r="E41" s="85"/>
+      <c r="F41" s="85"/>
+      <c r="G41" s="85"/>
+      <c r="H41" s="85"/>
+      <c r="I41" s="85"/>
+      <c r="J41" s="85"/>
+      <c r="K41" s="85"/>
+      <c r="L41" s="85"/>
+      <c r="M41" s="85"/>
+      <c r="N41" s="85"/>
+      <c r="O41" s="85"/>
+      <c r="P41" s="85"/>
+      <c r="Q41" s="85"/>
+      <c r="R41" s="85"/>
+      <c r="S41" s="85"/>
+      <c r="T41" s="85"/>
+      <c r="U41" s="85"/>
+      <c r="V41" s="85"/>
+      <c r="W41" s="85"/>
+      <c r="X41" s="85"/>
+      <c r="Y41" s="85"/>
+      <c r="Z41" s="85"/>
+      <c r="AA41" s="85"/>
+      <c r="AB41" s="85"/>
     </row>
     <row r="42" spans="2:28">
-      <c r="B42" s="83"/>
-      <c r="C42" s="83"/>
-      <c r="D42" s="83"/>
-      <c r="E42" s="83"/>
-      <c r="F42" s="83"/>
-      <c r="G42" s="83"/>
-      <c r="H42" s="83"/>
-      <c r="I42" s="83"/>
-      <c r="J42" s="83"/>
-      <c r="K42" s="83"/>
-      <c r="L42" s="83"/>
-      <c r="M42" s="83"/>
-      <c r="N42" s="83"/>
-      <c r="O42" s="83"/>
-      <c r="P42" s="83"/>
-      <c r="Q42" s="83"/>
-      <c r="R42" s="83"/>
-      <c r="S42" s="83"/>
-      <c r="T42" s="83"/>
-      <c r="U42" s="83"/>
-      <c r="V42" s="83"/>
-      <c r="W42" s="83"/>
-      <c r="X42" s="83"/>
-      <c r="Y42" s="83"/>
-      <c r="Z42" s="83"/>
-      <c r="AA42" s="83"/>
-      <c r="AB42" s="83"/>
+      <c r="B42" s="85"/>
+      <c r="C42" s="85"/>
+      <c r="D42" s="85"/>
+      <c r="E42" s="85"/>
+      <c r="F42" s="85"/>
+      <c r="G42" s="85"/>
+      <c r="H42" s="85"/>
+      <c r="I42" s="85"/>
+      <c r="J42" s="85"/>
+      <c r="K42" s="85"/>
+      <c r="L42" s="85"/>
+      <c r="M42" s="85"/>
+      <c r="N42" s="85"/>
+      <c r="O42" s="85"/>
+      <c r="P42" s="85"/>
+      <c r="Q42" s="85"/>
+      <c r="R42" s="85"/>
+      <c r="S42" s="85"/>
+      <c r="T42" s="85"/>
+      <c r="U42" s="85"/>
+      <c r="V42" s="85"/>
+      <c r="W42" s="85"/>
+      <c r="X42" s="85"/>
+      <c r="Y42" s="85"/>
+      <c r="Z42" s="85"/>
+      <c r="AA42" s="85"/>
+      <c r="AB42" s="85"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -30359,7 +31623,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet17"/>
   <dimension ref="E3:E5"/>
@@ -31428,11 +32692,11 @@
       <c r="F10" t="s">
         <v>56</v>
       </c>
-      <c r="J10" s="59" t="s">
+      <c r="J10" s="61" t="s">
         <v>53</v>
       </c>
-      <c r="K10" s="60"/>
-      <c r="L10" s="60"/>
+      <c r="K10" s="62"/>
+      <c r="L10" s="62"/>
       <c r="N10" t="s">
         <v>41</v>
       </c>
@@ -31459,12 +32723,12 @@
       <c r="M12" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="N12" s="58" t="s">
+      <c r="N12" s="60" t="s">
         <v>40</v>
       </c>
-      <c r="O12" s="58"/>
-      <c r="P12" s="58"/>
-      <c r="Q12" s="58"/>
+      <c r="O12" s="60"/>
+      <c r="P12" s="60"/>
+      <c r="Q12" s="60"/>
     </row>
     <row r="13" spans="1:17" ht="24">
       <c r="B13" s="2" t="s">
@@ -31777,16 +33041,16 @@
       </c>
     </row>
     <row r="14" spans="1:17" ht="18.75">
-      <c r="B14" s="61" t="s">
+      <c r="B14" s="63" t="s">
         <v>59</v>
       </c>
-      <c r="C14" s="61"/>
-      <c r="D14" s="61"/>
-      <c r="H14" s="61" t="s">
+      <c r="C14" s="63"/>
+      <c r="D14" s="63"/>
+      <c r="H14" s="63" t="s">
         <v>64</v>
       </c>
-      <c r="I14" s="61"/>
-      <c r="J14" s="61"/>
+      <c r="I14" s="63"/>
+      <c r="J14" s="63"/>
     </row>
     <row r="22" spans="2:17">
       <c r="B22" t="s">
